--- a/docs/StatusTracker.xlsx
+++ b/docs/StatusTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaushikyadala/Documents/IIIT/Fourth_Sem/DASS/project-monorepo-team-35/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20FC9D9-6CE9-CC41-9DF1-556393B49DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34692D71-1791-D042-B5D3-AED09E578EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="200" yWindow="1000" windowWidth="35600" windowHeight="22180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="54">
   <si>
     <t>PROJECT NUMBER</t>
   </si>
@@ -191,14 +191,17 @@
     <t>Draft and Categorize Requirements</t>
   </si>
   <si>
-    <t>Feasibility of competitors analysis</t>
+    <t>Feasibility of competitors analysis (META and LinkedIN)</t>
+  </si>
+  <si>
+    <t>META has endpoints for public access, LinkedIN would require scraping but that is a very iffy thing :(</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -257,6 +260,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -302,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -364,6 +375,11 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -589,8 +605,8 @@
     <col min="1" max="1" width="49.6640625" customWidth="1"/>
     <col min="2" max="2" width="73.5" customWidth="1"/>
     <col min="4" max="4" width="20.1640625" customWidth="1"/>
-    <col min="7" max="7" width="72.6640625" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="80.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" style="25" customWidth="1"/>
     <col min="9" max="9" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -601,7 +617,7 @@
       <c r="B1" s="2">
         <v>35</v>
       </c>
-      <c r="H1">
+      <c r="H1" s="25">
         <f>D:D-E:E</f>
         <v>0</v>
       </c>
@@ -644,7 +660,7 @@
       <c r="G4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="21" t="s">
         <v>12</v>
       </c>
       <c r="I4" s="5" t="s">
@@ -661,7 +677,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="8"/>
+      <c r="H5" s="21"/>
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -684,7 +700,7 @@
         <v>18</v>
       </c>
       <c r="G6" s="9"/>
-      <c r="H6" s="5">
+      <c r="H6" s="21">
         <f>D:D-E:E</f>
         <v>0.1</v>
       </c>
@@ -712,7 +728,7 @@
       <c r="G7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="21">
         <f>D:D-E:E</f>
         <v>0.5</v>
       </c>
@@ -738,7 +754,7 @@
         <v>18</v>
       </c>
       <c r="G8" s="9"/>
-      <c r="H8" s="5">
+      <c r="H8" s="21">
         <f>D:D-E:E</f>
         <v>0.25</v>
       </c>
@@ -764,7 +780,7 @@
         <v>18</v>
       </c>
       <c r="G9" s="9"/>
-      <c r="H9" s="5">
+      <c r="H9" s="21">
         <f>D:D-E:E</f>
         <v>0.5</v>
       </c>
@@ -790,7 +806,7 @@
         <v>18</v>
       </c>
       <c r="G10" s="9"/>
-      <c r="H10" s="5">
+      <c r="H10" s="21">
         <f>D:D-E:E</f>
         <v>0.2</v>
       </c>
@@ -818,7 +834,7 @@
       <c r="G11" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="21">
         <f>D:D-E:E</f>
         <v>0.5</v>
       </c>
@@ -834,7 +850,7 @@
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="5">
+      <c r="H12" s="21">
         <f>D:D-E:E</f>
         <v>0</v>
       </c>
@@ -860,7 +876,7 @@
         <v>18</v>
       </c>
       <c r="G13" s="9"/>
-      <c r="H13" s="5">
+      <c r="H13" s="21">
         <f>D:D-E:E</f>
         <v>9.9999999999999978E-2</v>
       </c>
@@ -886,7 +902,7 @@
         <v>18</v>
       </c>
       <c r="G14" s="9"/>
-      <c r="H14" s="5">
+      <c r="H14" s="21">
         <f>D:D-E:E</f>
         <v>0.2</v>
       </c>
@@ -902,7 +918,7 @@
       <c r="C15" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="21">
         <f>D:D-E:E</f>
         <v>0</v>
       </c>
@@ -927,7 +943,7 @@
         <v>18</v>
       </c>
       <c r="G16" s="9"/>
-      <c r="H16" s="5">
+      <c r="H16" s="21">
         <f>D:D-E:E</f>
         <v>4.9999999999999989E-2</v>
       </c>
@@ -955,7 +971,7 @@
       <c r="G17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="21">
         <f>D:D-E:E</f>
         <v>0.25</v>
       </c>
@@ -971,7 +987,7 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="5">
+      <c r="H18" s="21">
         <f>D:D-E:E</f>
         <v>0</v>
       </c>
@@ -999,7 +1015,7 @@
       <c r="G19" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="21">
         <f>D:D-E:E</f>
         <v>-0.25</v>
       </c>
@@ -1025,7 +1041,7 @@
         <v>18</v>
       </c>
       <c r="G20" s="9"/>
-      <c r="H20" s="5">
+      <c r="H20" s="21">
         <f>D:D-E:E</f>
         <v>0.2</v>
       </c>
@@ -1049,7 +1065,7 @@
         <v>38</v>
       </c>
       <c r="G21" s="9"/>
-      <c r="H21" s="5">
+      <c r="H21" s="21">
         <f>D:D-E:E</f>
         <v>0.75</v>
       </c>
@@ -1075,7 +1091,7 @@
         <v>18</v>
       </c>
       <c r="G22" s="9"/>
-      <c r="H22" s="5">
+      <c r="H22" s="21">
         <f>D:D-E:E</f>
         <v>0.25</v>
       </c>
@@ -1115,7 +1131,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="6"/>
-      <c r="H24" s="8"/>
+      <c r="H24" s="21"/>
       <c r="I24" s="8"/>
     </row>
     <row r="25" spans="1:26" ht="13" x14ac:dyDescent="0.15">
@@ -1130,7 +1146,7 @@
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="5"/>
+      <c r="H25" s="21"/>
       <c r="I25" s="8"/>
     </row>
     <row r="26" spans="1:26" ht="13" x14ac:dyDescent="0.15">
@@ -1149,7 +1165,7 @@
         <v>38</v>
       </c>
       <c r="G26" s="9"/>
-      <c r="H26" s="5"/>
+      <c r="H26" s="21"/>
       <c r="I26" s="14"/>
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
@@ -1185,7 +1201,7 @@
         <v>38</v>
       </c>
       <c r="G27" s="13"/>
-      <c r="H27" s="5"/>
+      <c r="H27" s="21"/>
       <c r="I27" s="14"/>
       <c r="J27" s="13"/>
       <c r="K27" s="13"/>
@@ -1221,7 +1237,7 @@
         <v>38</v>
       </c>
       <c r="G28" s="13"/>
-      <c r="H28" s="5"/>
+      <c r="H28" s="21"/>
       <c r="I28" s="14"/>
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
@@ -1259,7 +1275,7 @@
         <v>18</v>
       </c>
       <c r="G29" s="13"/>
-      <c r="H29" s="5">
+      <c r="H29" s="21">
         <f>D:D-E:E</f>
         <v>-0.5</v>
       </c>
@@ -1298,7 +1314,7 @@
         <v>38</v>
       </c>
       <c r="G30" s="13"/>
-      <c r="H30" s="5"/>
+      <c r="H30" s="21"/>
       <c r="I30" s="8"/>
     </row>
     <row r="31" spans="1:26" ht="13" x14ac:dyDescent="0.15">
@@ -1309,11 +1325,21 @@
       <c r="C31" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="12"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="5"/>
+      <c r="D31" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="E31" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="H31" s="21">
+        <v>0</v>
+      </c>
       <c r="I31" s="8"/>
     </row>
     <row r="32" spans="1:26" ht="13" x14ac:dyDescent="0.15">
@@ -1336,7 +1362,7 @@
         <v>38</v>
       </c>
       <c r="G32" s="9"/>
-      <c r="H32" s="8">
+      <c r="H32" s="21">
         <f>D:D-E:E</f>
         <v>0.5</v>
       </c>
@@ -1355,12 +1381,17 @@
       <c r="D33" s="10">
         <v>1.5</v>
       </c>
-      <c r="E33" s="10"/>
-      <c r="F33" s="20" t="s">
-        <v>38</v>
+      <c r="E33" s="10">
+        <v>1.75</v>
+      </c>
+      <c r="F33" s="24" t="s">
+        <v>18</v>
       </c>
       <c r="G33" s="9"/>
-      <c r="H33" s="8"/>
+      <c r="H33" s="21">
+        <f>D:D-E:E</f>
+        <v>-0.25</v>
+      </c>
       <c r="I33" s="8"/>
     </row>
     <row r="34" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1371,7 +1402,7 @@
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
       <c r="G34" s="9"/>
-      <c r="H34" s="8"/>
+      <c r="H34" s="21"/>
       <c r="I34" s="8"/>
     </row>
     <row r="35" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1382,7 +1413,7 @@
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
       <c r="G35" s="9"/>
-      <c r="H35" s="8"/>
+      <c r="H35" s="21"/>
       <c r="I35" s="8"/>
     </row>
     <row r="36" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1393,7 +1424,7 @@
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
       <c r="G36" s="9"/>
-      <c r="H36" s="8"/>
+      <c r="H36" s="21"/>
       <c r="I36" s="8"/>
     </row>
     <row r="37" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1404,7 +1435,7 @@
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
       <c r="G37" s="9"/>
-      <c r="H37" s="8"/>
+      <c r="H37" s="21"/>
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1415,7 +1446,7 @@
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
       <c r="G38" s="9"/>
-      <c r="H38" s="8"/>
+      <c r="H38" s="21"/>
       <c r="I38" s="8"/>
     </row>
     <row r="39" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1426,7 +1457,7 @@
       <c r="E39" s="10"/>
       <c r="F39" s="10"/>
       <c r="G39" s="9"/>
-      <c r="H39" s="8"/>
+      <c r="H39" s="21"/>
       <c r="I39" s="8"/>
     </row>
     <row r="40" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1437,7 +1468,7 @@
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
       <c r="G40" s="9"/>
-      <c r="H40" s="8"/>
+      <c r="H40" s="21"/>
       <c r="I40" s="8"/>
     </row>
     <row r="41" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1448,7 +1479,7 @@
       <c r="E41" s="10"/>
       <c r="F41" s="20"/>
       <c r="G41" s="9"/>
-      <c r="H41" s="8"/>
+      <c r="H41" s="21"/>
       <c r="I41" s="8"/>
     </row>
     <row r="42" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1459,7 +1490,7 @@
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
       <c r="G42" s="9"/>
-      <c r="H42" s="8"/>
+      <c r="H42" s="21"/>
       <c r="I42" s="8"/>
     </row>
     <row r="43" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1470,7 +1501,7 @@
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
       <c r="G43" s="9"/>
-      <c r="H43" s="8"/>
+      <c r="H43" s="21"/>
       <c r="I43" s="8"/>
     </row>
     <row r="44" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1481,7 +1512,7 @@
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
       <c r="G44" s="9"/>
-      <c r="H44" s="8"/>
+      <c r="H44" s="21"/>
       <c r="I44" s="8"/>
     </row>
     <row r="45" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1492,7 +1523,7 @@
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
       <c r="G45" s="9"/>
-      <c r="H45" s="8"/>
+      <c r="H45" s="21"/>
       <c r="I45" s="8"/>
     </row>
     <row r="46" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1503,7 +1534,7 @@
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
       <c r="G46" s="9"/>
-      <c r="H46" s="8"/>
+      <c r="H46" s="21"/>
       <c r="I46" s="8"/>
     </row>
     <row r="47" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1514,7 +1545,7 @@
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
       <c r="G47" s="9"/>
-      <c r="H47" s="8"/>
+      <c r="H47" s="21"/>
       <c r="I47" s="8"/>
     </row>
     <row r="48" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1525,7 +1556,7 @@
       <c r="E48" s="10"/>
       <c r="F48" s="10"/>
       <c r="G48" s="9"/>
-      <c r="H48" s="8"/>
+      <c r="H48" s="21"/>
       <c r="I48" s="8"/>
     </row>
     <row r="49" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1536,7 +1567,7 @@
       <c r="E49" s="10"/>
       <c r="F49" s="10"/>
       <c r="G49" s="9"/>
-      <c r="H49" s="8"/>
+      <c r="H49" s="21"/>
       <c r="I49" s="8"/>
     </row>
     <row r="50" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1547,7 +1578,7 @@
       <c r="E50" s="10"/>
       <c r="F50" s="10"/>
       <c r="G50" s="9"/>
-      <c r="H50" s="8"/>
+      <c r="H50" s="21"/>
       <c r="I50" s="8"/>
     </row>
     <row r="51" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1558,7 +1589,7 @@
       <c r="E51" s="10"/>
       <c r="F51" s="10"/>
       <c r="G51" s="9"/>
-      <c r="H51" s="8"/>
+      <c r="H51" s="21"/>
       <c r="I51" s="8"/>
     </row>
     <row r="52" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1569,7 +1600,7 @@
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
       <c r="G52" s="9"/>
-      <c r="H52" s="8"/>
+      <c r="H52" s="21"/>
       <c r="I52" s="8"/>
     </row>
     <row r="53" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1580,7 +1611,7 @@
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
       <c r="G53" s="9"/>
-      <c r="H53" s="8"/>
+      <c r="H53" s="21"/>
       <c r="I53" s="8"/>
     </row>
     <row r="54" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1591,7 +1622,7 @@
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
       <c r="G54" s="9"/>
-      <c r="H54" s="8"/>
+      <c r="H54" s="21"/>
       <c r="I54" s="8"/>
     </row>
     <row r="55" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1602,7 +1633,7 @@
       <c r="E55" s="10"/>
       <c r="F55" s="10"/>
       <c r="G55" s="9"/>
-      <c r="H55" s="8"/>
+      <c r="H55" s="21"/>
       <c r="I55" s="8"/>
     </row>
     <row r="56" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1613,7 +1644,7 @@
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
       <c r="G56" s="9"/>
-      <c r="H56" s="8"/>
+      <c r="H56" s="21"/>
       <c r="I56" s="8"/>
     </row>
     <row r="57" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1624,7 +1655,7 @@
       <c r="E57" s="10"/>
       <c r="F57" s="10"/>
       <c r="G57" s="9"/>
-      <c r="H57" s="8"/>
+      <c r="H57" s="21"/>
       <c r="I57" s="8"/>
     </row>
     <row r="58" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1635,7 +1666,7 @@
       <c r="E58" s="10"/>
       <c r="F58" s="10"/>
       <c r="G58" s="9"/>
-      <c r="H58" s="8"/>
+      <c r="H58" s="21"/>
       <c r="I58" s="8"/>
     </row>
     <row r="59" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1646,7 +1677,7 @@
       <c r="E59" s="10"/>
       <c r="F59" s="10"/>
       <c r="G59" s="9"/>
-      <c r="H59" s="8"/>
+      <c r="H59" s="21"/>
       <c r="I59" s="8"/>
     </row>
     <row r="60" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1657,7 +1688,7 @@
       <c r="E60" s="10"/>
       <c r="F60" s="10"/>
       <c r="G60" s="9"/>
-      <c r="H60" s="8"/>
+      <c r="H60" s="21"/>
       <c r="I60" s="8"/>
     </row>
     <row r="61" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1668,7 +1699,7 @@
       <c r="E61" s="10"/>
       <c r="F61" s="10"/>
       <c r="G61" s="9"/>
-      <c r="H61" s="8"/>
+      <c r="H61" s="21"/>
       <c r="I61" s="8"/>
     </row>
     <row r="62" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1679,7 +1710,7 @@
       <c r="E62" s="10"/>
       <c r="F62" s="10"/>
       <c r="G62" s="9"/>
-      <c r="H62" s="8"/>
+      <c r="H62" s="21"/>
       <c r="I62" s="8"/>
     </row>
     <row r="63" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1690,7 +1721,7 @@
       <c r="E63" s="10"/>
       <c r="F63" s="10"/>
       <c r="G63" s="9"/>
-      <c r="H63" s="8"/>
+      <c r="H63" s="21"/>
       <c r="I63" s="8"/>
     </row>
     <row r="64" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1701,7 +1732,7 @@
       <c r="E64" s="10"/>
       <c r="F64" s="10"/>
       <c r="G64" s="9"/>
-      <c r="H64" s="8"/>
+      <c r="H64" s="21"/>
       <c r="I64" s="8"/>
     </row>
     <row r="65" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1712,7 +1743,7 @@
       <c r="E65" s="10"/>
       <c r="F65" s="10"/>
       <c r="G65" s="9"/>
-      <c r="H65" s="8"/>
+      <c r="H65" s="21"/>
       <c r="I65" s="8"/>
     </row>
     <row r="66" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1723,7 +1754,7 @@
       <c r="E66" s="10"/>
       <c r="F66" s="10"/>
       <c r="G66" s="9"/>
-      <c r="H66" s="8"/>
+      <c r="H66" s="21"/>
       <c r="I66" s="8"/>
     </row>
     <row r="67" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1734,7 +1765,7 @@
       <c r="E67" s="10"/>
       <c r="F67" s="10"/>
       <c r="G67" s="9"/>
-      <c r="H67" s="8"/>
+      <c r="H67" s="21"/>
       <c r="I67" s="8"/>
     </row>
     <row r="68" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1745,7 +1776,7 @@
       <c r="E68" s="10"/>
       <c r="F68" s="10"/>
       <c r="G68" s="9"/>
-      <c r="H68" s="8"/>
+      <c r="H68" s="21"/>
       <c r="I68" s="8"/>
     </row>
     <row r="69" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1756,7 +1787,7 @@
       <c r="E69" s="10"/>
       <c r="F69" s="10"/>
       <c r="G69" s="9"/>
-      <c r="H69" s="8"/>
+      <c r="H69" s="21"/>
       <c r="I69" s="8"/>
     </row>
     <row r="70" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1767,7 +1798,7 @@
       <c r="E70" s="10"/>
       <c r="F70" s="10"/>
       <c r="G70" s="9"/>
-      <c r="H70" s="8"/>
+      <c r="H70" s="21"/>
       <c r="I70" s="8"/>
     </row>
     <row r="71" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1778,7 +1809,7 @@
       <c r="E71" s="10"/>
       <c r="F71" s="10"/>
       <c r="G71" s="9"/>
-      <c r="H71" s="8"/>
+      <c r="H71" s="21"/>
       <c r="I71" s="8"/>
     </row>
     <row r="72" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1789,7 +1820,7 @@
       <c r="E72" s="10"/>
       <c r="F72" s="10"/>
       <c r="G72" s="9"/>
-      <c r="H72" s="8"/>
+      <c r="H72" s="21"/>
       <c r="I72" s="8"/>
     </row>
     <row r="73" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1800,7 +1831,7 @@
       <c r="E73" s="10"/>
       <c r="F73" s="10"/>
       <c r="G73" s="9"/>
-      <c r="H73" s="8"/>
+      <c r="H73" s="21"/>
       <c r="I73" s="8"/>
     </row>
     <row r="74" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1811,7 +1842,7 @@
       <c r="E74" s="10"/>
       <c r="F74" s="10"/>
       <c r="G74" s="9"/>
-      <c r="H74" s="8"/>
+      <c r="H74" s="21"/>
       <c r="I74" s="8"/>
     </row>
     <row r="75" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1822,7 +1853,7 @@
       <c r="E75" s="10"/>
       <c r="F75" s="10"/>
       <c r="G75" s="9"/>
-      <c r="H75" s="8"/>
+      <c r="H75" s="21"/>
       <c r="I75" s="8"/>
     </row>
     <row r="76" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1833,7 +1864,7 @@
       <c r="E76" s="10"/>
       <c r="F76" s="10"/>
       <c r="G76" s="9"/>
-      <c r="H76" s="8"/>
+      <c r="H76" s="21"/>
       <c r="I76" s="8"/>
     </row>
     <row r="77" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1844,7 +1875,7 @@
       <c r="E77" s="10"/>
       <c r="F77" s="10"/>
       <c r="G77" s="9"/>
-      <c r="H77" s="8"/>
+      <c r="H77" s="21"/>
       <c r="I77" s="8"/>
     </row>
     <row r="78" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1855,7 +1886,7 @@
       <c r="E78" s="10"/>
       <c r="F78" s="10"/>
       <c r="G78" s="9"/>
-      <c r="H78" s="8"/>
+      <c r="H78" s="21"/>
       <c r="I78" s="8"/>
     </row>
     <row r="79" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1866,7 +1897,7 @@
       <c r="E79" s="10"/>
       <c r="F79" s="10"/>
       <c r="G79" s="9"/>
-      <c r="H79" s="8"/>
+      <c r="H79" s="21"/>
       <c r="I79" s="8"/>
     </row>
     <row r="80" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1877,7 +1908,7 @@
       <c r="E80" s="10"/>
       <c r="F80" s="10"/>
       <c r="G80" s="9"/>
-      <c r="H80" s="8"/>
+      <c r="H80" s="21"/>
       <c r="I80" s="8"/>
     </row>
     <row r="81" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1888,7 +1919,7 @@
       <c r="E81" s="10"/>
       <c r="F81" s="10"/>
       <c r="G81" s="9"/>
-      <c r="H81" s="8"/>
+      <c r="H81" s="21"/>
       <c r="I81" s="8"/>
     </row>
     <row r="82" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1899,7 +1930,7 @@
       <c r="E82" s="10"/>
       <c r="F82" s="10"/>
       <c r="G82" s="9"/>
-      <c r="H82" s="8"/>
+      <c r="H82" s="21"/>
       <c r="I82" s="8"/>
     </row>
     <row r="83" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1910,7 +1941,7 @@
       <c r="E83" s="10"/>
       <c r="F83" s="10"/>
       <c r="G83" s="9"/>
-      <c r="H83" s="8"/>
+      <c r="H83" s="21"/>
       <c r="I83" s="8"/>
     </row>
     <row r="84" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1921,7 +1952,7 @@
       <c r="E84" s="10"/>
       <c r="F84" s="10"/>
       <c r="G84" s="9"/>
-      <c r="H84" s="8"/>
+      <c r="H84" s="21"/>
       <c r="I84" s="8"/>
     </row>
     <row r="85" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1932,7 +1963,7 @@
       <c r="E85" s="10"/>
       <c r="F85" s="10"/>
       <c r="G85" s="9"/>
-      <c r="H85" s="8"/>
+      <c r="H85" s="21"/>
       <c r="I85" s="8"/>
     </row>
     <row r="86" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1943,7 +1974,7 @@
       <c r="E86" s="10"/>
       <c r="F86" s="10"/>
       <c r="G86" s="9"/>
-      <c r="H86" s="8"/>
+      <c r="H86" s="21"/>
       <c r="I86" s="8"/>
     </row>
     <row r="87" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1954,7 +1985,7 @@
       <c r="E87" s="10"/>
       <c r="F87" s="10"/>
       <c r="G87" s="9"/>
-      <c r="H87" s="8"/>
+      <c r="H87" s="21"/>
       <c r="I87" s="8"/>
     </row>
     <row r="88" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1965,7 +1996,7 @@
       <c r="E88" s="10"/>
       <c r="F88" s="10"/>
       <c r="G88" s="9"/>
-      <c r="H88" s="8"/>
+      <c r="H88" s="21"/>
       <c r="I88" s="8"/>
     </row>
     <row r="89" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1976,7 +2007,7 @@
       <c r="E89" s="10"/>
       <c r="F89" s="10"/>
       <c r="G89" s="9"/>
-      <c r="H89" s="8"/>
+      <c r="H89" s="21"/>
       <c r="I89" s="8"/>
     </row>
     <row r="90" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1987,7 +2018,7 @@
       <c r="E90" s="10"/>
       <c r="F90" s="10"/>
       <c r="G90" s="9"/>
-      <c r="H90" s="8"/>
+      <c r="H90" s="21"/>
       <c r="I90" s="8"/>
     </row>
     <row r="91" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -1998,7 +2029,7 @@
       <c r="E91" s="10"/>
       <c r="F91" s="10"/>
       <c r="G91" s="9"/>
-      <c r="H91" s="8"/>
+      <c r="H91" s="21"/>
       <c r="I91" s="8"/>
     </row>
     <row r="92" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2009,7 +2040,7 @@
       <c r="E92" s="10"/>
       <c r="F92" s="10"/>
       <c r="G92" s="9"/>
-      <c r="H92" s="8"/>
+      <c r="H92" s="21"/>
       <c r="I92" s="8"/>
     </row>
     <row r="93" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2020,7 +2051,7 @@
       <c r="E93" s="10"/>
       <c r="F93" s="10"/>
       <c r="G93" s="9"/>
-      <c r="H93" s="8"/>
+      <c r="H93" s="21"/>
       <c r="I93" s="8"/>
     </row>
     <row r="94" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2031,7 +2062,7 @@
       <c r="E94" s="10"/>
       <c r="F94" s="10"/>
       <c r="G94" s="9"/>
-      <c r="H94" s="8"/>
+      <c r="H94" s="21"/>
       <c r="I94" s="8"/>
     </row>
     <row r="95" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2042,7 +2073,7 @@
       <c r="E95" s="10"/>
       <c r="F95" s="10"/>
       <c r="G95" s="9"/>
-      <c r="H95" s="8"/>
+      <c r="H95" s="21"/>
       <c r="I95" s="8"/>
     </row>
     <row r="96" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2053,7 +2084,7 @@
       <c r="E96" s="10"/>
       <c r="F96" s="10"/>
       <c r="G96" s="9"/>
-      <c r="H96" s="8"/>
+      <c r="H96" s="21"/>
       <c r="I96" s="8"/>
     </row>
     <row r="97" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2064,7 +2095,7 @@
       <c r="E97" s="10"/>
       <c r="F97" s="10"/>
       <c r="G97" s="9"/>
-      <c r="H97" s="8"/>
+      <c r="H97" s="21"/>
       <c r="I97" s="8"/>
     </row>
     <row r="98" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2075,7 +2106,7 @@
       <c r="E98" s="10"/>
       <c r="F98" s="10"/>
       <c r="G98" s="9"/>
-      <c r="H98" s="8"/>
+      <c r="H98" s="21"/>
       <c r="I98" s="8"/>
     </row>
     <row r="99" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2086,7 +2117,7 @@
       <c r="E99" s="10"/>
       <c r="F99" s="10"/>
       <c r="G99" s="9"/>
-      <c r="H99" s="8"/>
+      <c r="H99" s="21"/>
       <c r="I99" s="8"/>
     </row>
     <row r="100" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2097,7 +2128,7 @@
       <c r="E100" s="10"/>
       <c r="F100" s="10"/>
       <c r="G100" s="9"/>
-      <c r="H100" s="8"/>
+      <c r="H100" s="21"/>
       <c r="I100" s="8"/>
     </row>
     <row r="101" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2108,7 +2139,7 @@
       <c r="E101" s="10"/>
       <c r="F101" s="10"/>
       <c r="G101" s="9"/>
-      <c r="H101" s="8"/>
+      <c r="H101" s="21"/>
       <c r="I101" s="8"/>
     </row>
     <row r="102" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2119,7 +2150,7 @@
       <c r="E102" s="10"/>
       <c r="F102" s="10"/>
       <c r="G102" s="9"/>
-      <c r="H102" s="8"/>
+      <c r="H102" s="21"/>
       <c r="I102" s="8"/>
     </row>
     <row r="103" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2130,7 +2161,7 @@
       <c r="E103" s="10"/>
       <c r="F103" s="10"/>
       <c r="G103" s="9"/>
-      <c r="H103" s="8"/>
+      <c r="H103" s="21"/>
       <c r="I103" s="8"/>
     </row>
     <row r="104" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2141,7 +2172,7 @@
       <c r="E104" s="10"/>
       <c r="F104" s="10"/>
       <c r="G104" s="9"/>
-      <c r="H104" s="8"/>
+      <c r="H104" s="21"/>
       <c r="I104" s="8"/>
     </row>
     <row r="105" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2152,7 +2183,7 @@
       <c r="E105" s="10"/>
       <c r="F105" s="10"/>
       <c r="G105" s="9"/>
-      <c r="H105" s="8"/>
+      <c r="H105" s="21"/>
       <c r="I105" s="8"/>
     </row>
     <row r="106" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2163,7 +2194,7 @@
       <c r="E106" s="10"/>
       <c r="F106" s="10"/>
       <c r="G106" s="9"/>
-      <c r="H106" s="8"/>
+      <c r="H106" s="21"/>
       <c r="I106" s="8"/>
     </row>
     <row r="107" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2174,7 +2205,7 @@
       <c r="E107" s="10"/>
       <c r="F107" s="10"/>
       <c r="G107" s="9"/>
-      <c r="H107" s="8"/>
+      <c r="H107" s="21"/>
       <c r="I107" s="8"/>
     </row>
     <row r="108" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2185,7 +2216,7 @@
       <c r="E108" s="10"/>
       <c r="F108" s="10"/>
       <c r="G108" s="9"/>
-      <c r="H108" s="8"/>
+      <c r="H108" s="21"/>
       <c r="I108" s="8"/>
     </row>
     <row r="109" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2196,7 +2227,7 @@
       <c r="E109" s="10"/>
       <c r="F109" s="10"/>
       <c r="G109" s="9"/>
-      <c r="H109" s="8"/>
+      <c r="H109" s="21"/>
       <c r="I109" s="8"/>
     </row>
     <row r="110" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2207,7 +2238,7 @@
       <c r="E110" s="10"/>
       <c r="F110" s="10"/>
       <c r="G110" s="9"/>
-      <c r="H110" s="8"/>
+      <c r="H110" s="21"/>
       <c r="I110" s="8"/>
     </row>
     <row r="111" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2218,7 +2249,7 @@
       <c r="E111" s="10"/>
       <c r="F111" s="10"/>
       <c r="G111" s="9"/>
-      <c r="H111" s="8"/>
+      <c r="H111" s="21"/>
       <c r="I111" s="8"/>
     </row>
     <row r="112" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2229,7 +2260,7 @@
       <c r="E112" s="10"/>
       <c r="F112" s="10"/>
       <c r="G112" s="9"/>
-      <c r="H112" s="8"/>
+      <c r="H112" s="21"/>
       <c r="I112" s="8"/>
     </row>
     <row r="113" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2240,7 +2271,7 @@
       <c r="E113" s="10"/>
       <c r="F113" s="10"/>
       <c r="G113" s="9"/>
-      <c r="H113" s="8"/>
+      <c r="H113" s="21"/>
       <c r="I113" s="8"/>
     </row>
     <row r="114" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2251,7 +2282,7 @@
       <c r="E114" s="10"/>
       <c r="F114" s="10"/>
       <c r="G114" s="9"/>
-      <c r="H114" s="8"/>
+      <c r="H114" s="21"/>
       <c r="I114" s="8"/>
     </row>
     <row r="115" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2262,7 +2293,7 @@
       <c r="E115" s="10"/>
       <c r="F115" s="10"/>
       <c r="G115" s="9"/>
-      <c r="H115" s="8"/>
+      <c r="H115" s="21"/>
       <c r="I115" s="8"/>
     </row>
     <row r="116" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2273,7 +2304,7 @@
       <c r="E116" s="10"/>
       <c r="F116" s="10"/>
       <c r="G116" s="9"/>
-      <c r="H116" s="8"/>
+      <c r="H116" s="21"/>
       <c r="I116" s="8"/>
     </row>
     <row r="117" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2284,7 +2315,7 @@
       <c r="E117" s="10"/>
       <c r="F117" s="10"/>
       <c r="G117" s="9"/>
-      <c r="H117" s="8"/>
+      <c r="H117" s="21"/>
       <c r="I117" s="8"/>
     </row>
     <row r="118" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2295,7 +2326,7 @@
       <c r="E118" s="10"/>
       <c r="F118" s="10"/>
       <c r="G118" s="9"/>
-      <c r="H118" s="8"/>
+      <c r="H118" s="21"/>
       <c r="I118" s="8"/>
     </row>
     <row r="119" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2306,7 +2337,7 @@
       <c r="E119" s="10"/>
       <c r="F119" s="10"/>
       <c r="G119" s="9"/>
-      <c r="H119" s="8"/>
+      <c r="H119" s="21"/>
       <c r="I119" s="8"/>
     </row>
     <row r="120" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2317,7 +2348,7 @@
       <c r="E120" s="10"/>
       <c r="F120" s="10"/>
       <c r="G120" s="9"/>
-      <c r="H120" s="8"/>
+      <c r="H120" s="21"/>
       <c r="I120" s="8"/>
     </row>
     <row r="121" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2328,7 +2359,7 @@
       <c r="E121" s="10"/>
       <c r="F121" s="10"/>
       <c r="G121" s="9"/>
-      <c r="H121" s="8"/>
+      <c r="H121" s="21"/>
       <c r="I121" s="8"/>
     </row>
     <row r="122" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2339,7 +2370,7 @@
       <c r="E122" s="10"/>
       <c r="F122" s="10"/>
       <c r="G122" s="9"/>
-      <c r="H122" s="8"/>
+      <c r="H122" s="21"/>
       <c r="I122" s="8"/>
     </row>
     <row r="123" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2350,7 +2381,7 @@
       <c r="E123" s="10"/>
       <c r="F123" s="10"/>
       <c r="G123" s="9"/>
-      <c r="H123" s="8"/>
+      <c r="H123" s="21"/>
       <c r="I123" s="8"/>
     </row>
     <row r="124" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2361,7 +2392,7 @@
       <c r="E124" s="10"/>
       <c r="F124" s="10"/>
       <c r="G124" s="9"/>
-      <c r="H124" s="8"/>
+      <c r="H124" s="21"/>
       <c r="I124" s="8"/>
     </row>
     <row r="125" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2372,7 +2403,7 @@
       <c r="E125" s="10"/>
       <c r="F125" s="10"/>
       <c r="G125" s="9"/>
-      <c r="H125" s="8"/>
+      <c r="H125" s="21"/>
       <c r="I125" s="8"/>
     </row>
     <row r="126" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2383,7 +2414,7 @@
       <c r="E126" s="10"/>
       <c r="F126" s="10"/>
       <c r="G126" s="9"/>
-      <c r="H126" s="8"/>
+      <c r="H126" s="21"/>
       <c r="I126" s="8"/>
     </row>
     <row r="127" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2394,7 +2425,7 @@
       <c r="E127" s="10"/>
       <c r="F127" s="10"/>
       <c r="G127" s="9"/>
-      <c r="H127" s="8"/>
+      <c r="H127" s="21"/>
       <c r="I127" s="8"/>
     </row>
     <row r="128" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2405,7 +2436,7 @@
       <c r="E128" s="10"/>
       <c r="F128" s="10"/>
       <c r="G128" s="9"/>
-      <c r="H128" s="8"/>
+      <c r="H128" s="21"/>
       <c r="I128" s="8"/>
     </row>
     <row r="129" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2416,7 +2447,7 @@
       <c r="E129" s="10"/>
       <c r="F129" s="10"/>
       <c r="G129" s="9"/>
-      <c r="H129" s="8"/>
+      <c r="H129" s="21"/>
       <c r="I129" s="8"/>
     </row>
     <row r="130" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2427,7 +2458,7 @@
       <c r="E130" s="10"/>
       <c r="F130" s="10"/>
       <c r="G130" s="9"/>
-      <c r="H130" s="8"/>
+      <c r="H130" s="21"/>
       <c r="I130" s="8"/>
     </row>
     <row r="131" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2438,7 +2469,7 @@
       <c r="E131" s="10"/>
       <c r="F131" s="10"/>
       <c r="G131" s="9"/>
-      <c r="H131" s="8"/>
+      <c r="H131" s="21"/>
       <c r="I131" s="8"/>
     </row>
     <row r="132" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2449,7 +2480,7 @@
       <c r="E132" s="10"/>
       <c r="F132" s="10"/>
       <c r="G132" s="9"/>
-      <c r="H132" s="8"/>
+      <c r="H132" s="21"/>
       <c r="I132" s="8"/>
     </row>
     <row r="133" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2460,7 +2491,7 @@
       <c r="E133" s="10"/>
       <c r="F133" s="10"/>
       <c r="G133" s="9"/>
-      <c r="H133" s="8"/>
+      <c r="H133" s="21"/>
       <c r="I133" s="8"/>
     </row>
     <row r="134" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2471,7 +2502,7 @@
       <c r="E134" s="10"/>
       <c r="F134" s="10"/>
       <c r="G134" s="9"/>
-      <c r="H134" s="8"/>
+      <c r="H134" s="21"/>
       <c r="I134" s="8"/>
     </row>
     <row r="135" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2482,7 +2513,7 @@
       <c r="E135" s="10"/>
       <c r="F135" s="10"/>
       <c r="G135" s="9"/>
-      <c r="H135" s="8"/>
+      <c r="H135" s="21"/>
       <c r="I135" s="8"/>
     </row>
     <row r="136" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2493,7 +2524,7 @@
       <c r="E136" s="10"/>
       <c r="F136" s="10"/>
       <c r="G136" s="9"/>
-      <c r="H136" s="8"/>
+      <c r="H136" s="21"/>
       <c r="I136" s="8"/>
     </row>
     <row r="137" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2504,7 +2535,7 @@
       <c r="E137" s="10"/>
       <c r="F137" s="10"/>
       <c r="G137" s="9"/>
-      <c r="H137" s="8"/>
+      <c r="H137" s="21"/>
       <c r="I137" s="8"/>
     </row>
     <row r="138" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2515,7 +2546,7 @@
       <c r="E138" s="10"/>
       <c r="F138" s="10"/>
       <c r="G138" s="9"/>
-      <c r="H138" s="8"/>
+      <c r="H138" s="21"/>
       <c r="I138" s="8"/>
     </row>
     <row r="139" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2526,7 +2557,7 @@
       <c r="E139" s="10"/>
       <c r="F139" s="10"/>
       <c r="G139" s="9"/>
-      <c r="H139" s="8"/>
+      <c r="H139" s="21"/>
       <c r="I139" s="8"/>
     </row>
     <row r="140" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2537,7 +2568,7 @@
       <c r="E140" s="10"/>
       <c r="F140" s="10"/>
       <c r="G140" s="9"/>
-      <c r="H140" s="8"/>
+      <c r="H140" s="21"/>
       <c r="I140" s="8"/>
     </row>
     <row r="141" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2548,7 +2579,7 @@
       <c r="E141" s="10"/>
       <c r="F141" s="10"/>
       <c r="G141" s="9"/>
-      <c r="H141" s="8"/>
+      <c r="H141" s="21"/>
       <c r="I141" s="8"/>
     </row>
     <row r="142" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2559,7 +2590,7 @@
       <c r="E142" s="10"/>
       <c r="F142" s="10"/>
       <c r="G142" s="9"/>
-      <c r="H142" s="8"/>
+      <c r="H142" s="21"/>
       <c r="I142" s="8"/>
     </row>
     <row r="143" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2570,7 +2601,7 @@
       <c r="E143" s="10"/>
       <c r="F143" s="10"/>
       <c r="G143" s="9"/>
-      <c r="H143" s="8"/>
+      <c r="H143" s="21"/>
       <c r="I143" s="8"/>
     </row>
     <row r="144" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2581,7 +2612,7 @@
       <c r="E144" s="10"/>
       <c r="F144" s="10"/>
       <c r="G144" s="9"/>
-      <c r="H144" s="8"/>
+      <c r="H144" s="21"/>
       <c r="I144" s="8"/>
     </row>
     <row r="145" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2592,7 +2623,7 @@
       <c r="E145" s="10"/>
       <c r="F145" s="10"/>
       <c r="G145" s="9"/>
-      <c r="H145" s="8"/>
+      <c r="H145" s="21"/>
       <c r="I145" s="8"/>
     </row>
     <row r="146" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2603,7 +2634,7 @@
       <c r="E146" s="10"/>
       <c r="F146" s="10"/>
       <c r="G146" s="9"/>
-      <c r="H146" s="8"/>
+      <c r="H146" s="21"/>
       <c r="I146" s="8"/>
     </row>
     <row r="147" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2614,7 +2645,7 @@
       <c r="E147" s="10"/>
       <c r="F147" s="10"/>
       <c r="G147" s="9"/>
-      <c r="H147" s="8"/>
+      <c r="H147" s="21"/>
       <c r="I147" s="8"/>
     </row>
     <row r="148" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2625,7 +2656,7 @@
       <c r="E148" s="10"/>
       <c r="F148" s="10"/>
       <c r="G148" s="9"/>
-      <c r="H148" s="8"/>
+      <c r="H148" s="21"/>
       <c r="I148" s="8"/>
     </row>
     <row r="149" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2636,7 +2667,7 @@
       <c r="E149" s="10"/>
       <c r="F149" s="10"/>
       <c r="G149" s="9"/>
-      <c r="H149" s="8"/>
+      <c r="H149" s="21"/>
       <c r="I149" s="8"/>
     </row>
     <row r="150" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2647,7 +2678,7 @@
       <c r="E150" s="10"/>
       <c r="F150" s="10"/>
       <c r="G150" s="9"/>
-      <c r="H150" s="8"/>
+      <c r="H150" s="21"/>
       <c r="I150" s="8"/>
     </row>
     <row r="151" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2658,7 +2689,7 @@
       <c r="E151" s="10"/>
       <c r="F151" s="10"/>
       <c r="G151" s="9"/>
-      <c r="H151" s="8"/>
+      <c r="H151" s="21"/>
       <c r="I151" s="8"/>
     </row>
     <row r="152" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2669,7 +2700,7 @@
       <c r="E152" s="10"/>
       <c r="F152" s="10"/>
       <c r="G152" s="9"/>
-      <c r="H152" s="8"/>
+      <c r="H152" s="21"/>
       <c r="I152" s="8"/>
     </row>
     <row r="153" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2680,7 +2711,7 @@
       <c r="E153" s="10"/>
       <c r="F153" s="10"/>
       <c r="G153" s="9"/>
-      <c r="H153" s="8"/>
+      <c r="H153" s="21"/>
       <c r="I153" s="8"/>
     </row>
     <row r="154" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2691,7 +2722,7 @@
       <c r="E154" s="10"/>
       <c r="F154" s="10"/>
       <c r="G154" s="9"/>
-      <c r="H154" s="8"/>
+      <c r="H154" s="21"/>
       <c r="I154" s="8"/>
     </row>
     <row r="155" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2702,7 +2733,7 @@
       <c r="E155" s="10"/>
       <c r="F155" s="10"/>
       <c r="G155" s="9"/>
-      <c r="H155" s="8"/>
+      <c r="H155" s="21"/>
       <c r="I155" s="8"/>
     </row>
     <row r="156" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2713,7 +2744,7 @@
       <c r="E156" s="10"/>
       <c r="F156" s="10"/>
       <c r="G156" s="9"/>
-      <c r="H156" s="8"/>
+      <c r="H156" s="21"/>
       <c r="I156" s="8"/>
     </row>
     <row r="157" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2724,7 +2755,7 @@
       <c r="E157" s="10"/>
       <c r="F157" s="10"/>
       <c r="G157" s="9"/>
-      <c r="H157" s="8"/>
+      <c r="H157" s="21"/>
       <c r="I157" s="8"/>
     </row>
     <row r="158" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2735,7 +2766,7 @@
       <c r="E158" s="10"/>
       <c r="F158" s="10"/>
       <c r="G158" s="9"/>
-      <c r="H158" s="8"/>
+      <c r="H158" s="21"/>
       <c r="I158" s="8"/>
     </row>
     <row r="159" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2746,7 +2777,7 @@
       <c r="E159" s="10"/>
       <c r="F159" s="10"/>
       <c r="G159" s="9"/>
-      <c r="H159" s="8"/>
+      <c r="H159" s="21"/>
       <c r="I159" s="8"/>
     </row>
     <row r="160" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2757,7 +2788,7 @@
       <c r="E160" s="10"/>
       <c r="F160" s="10"/>
       <c r="G160" s="9"/>
-      <c r="H160" s="8"/>
+      <c r="H160" s="21"/>
       <c r="I160" s="8"/>
     </row>
     <row r="161" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2768,7 +2799,7 @@
       <c r="E161" s="10"/>
       <c r="F161" s="10"/>
       <c r="G161" s="9"/>
-      <c r="H161" s="8"/>
+      <c r="H161" s="21"/>
       <c r="I161" s="8"/>
     </row>
     <row r="162" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2779,7 +2810,7 @@
       <c r="E162" s="10"/>
       <c r="F162" s="10"/>
       <c r="G162" s="9"/>
-      <c r="H162" s="8"/>
+      <c r="H162" s="21"/>
       <c r="I162" s="8"/>
     </row>
     <row r="163" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2790,7 +2821,7 @@
       <c r="E163" s="10"/>
       <c r="F163" s="10"/>
       <c r="G163" s="9"/>
-      <c r="H163" s="8"/>
+      <c r="H163" s="21"/>
       <c r="I163" s="8"/>
     </row>
     <row r="164" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2801,7 +2832,7 @@
       <c r="E164" s="10"/>
       <c r="F164" s="10"/>
       <c r="G164" s="9"/>
-      <c r="H164" s="8"/>
+      <c r="H164" s="21"/>
       <c r="I164" s="8"/>
     </row>
     <row r="165" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2812,7 +2843,7 @@
       <c r="E165" s="10"/>
       <c r="F165" s="10"/>
       <c r="G165" s="9"/>
-      <c r="H165" s="8"/>
+      <c r="H165" s="21"/>
       <c r="I165" s="8"/>
     </row>
     <row r="166" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2823,7 +2854,7 @@
       <c r="E166" s="10"/>
       <c r="F166" s="10"/>
       <c r="G166" s="9"/>
-      <c r="H166" s="8"/>
+      <c r="H166" s="21"/>
       <c r="I166" s="8"/>
     </row>
     <row r="167" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2834,7 +2865,7 @@
       <c r="E167" s="10"/>
       <c r="F167" s="10"/>
       <c r="G167" s="9"/>
-      <c r="H167" s="8"/>
+      <c r="H167" s="21"/>
       <c r="I167" s="8"/>
     </row>
     <row r="168" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2845,7 +2876,7 @@
       <c r="E168" s="10"/>
       <c r="F168" s="10"/>
       <c r="G168" s="9"/>
-      <c r="H168" s="8"/>
+      <c r="H168" s="21"/>
       <c r="I168" s="8"/>
     </row>
     <row r="169" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2856,7 +2887,7 @@
       <c r="E169" s="10"/>
       <c r="F169" s="10"/>
       <c r="G169" s="9"/>
-      <c r="H169" s="8"/>
+      <c r="H169" s="21"/>
       <c r="I169" s="8"/>
     </row>
     <row r="170" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2867,7 +2898,7 @@
       <c r="E170" s="10"/>
       <c r="F170" s="10"/>
       <c r="G170" s="9"/>
-      <c r="H170" s="8"/>
+      <c r="H170" s="21"/>
       <c r="I170" s="8"/>
     </row>
     <row r="171" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2878,7 +2909,7 @@
       <c r="E171" s="10"/>
       <c r="F171" s="10"/>
       <c r="G171" s="9"/>
-      <c r="H171" s="8"/>
+      <c r="H171" s="21"/>
       <c r="I171" s="8"/>
     </row>
     <row r="172" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2889,7 +2920,7 @@
       <c r="E172" s="10"/>
       <c r="F172" s="10"/>
       <c r="G172" s="9"/>
-      <c r="H172" s="8"/>
+      <c r="H172" s="21"/>
       <c r="I172" s="8"/>
     </row>
     <row r="173" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2900,7 +2931,7 @@
       <c r="E173" s="10"/>
       <c r="F173" s="10"/>
       <c r="G173" s="9"/>
-      <c r="H173" s="8"/>
+      <c r="H173" s="21"/>
       <c r="I173" s="8"/>
     </row>
     <row r="174" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2911,7 +2942,7 @@
       <c r="E174" s="10"/>
       <c r="F174" s="10"/>
       <c r="G174" s="9"/>
-      <c r="H174" s="8"/>
+      <c r="H174" s="21"/>
       <c r="I174" s="8"/>
     </row>
     <row r="175" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2922,7 +2953,7 @@
       <c r="E175" s="10"/>
       <c r="F175" s="10"/>
       <c r="G175" s="9"/>
-      <c r="H175" s="8"/>
+      <c r="H175" s="21"/>
       <c r="I175" s="8"/>
     </row>
     <row r="176" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2933,7 +2964,7 @@
       <c r="E176" s="10"/>
       <c r="F176" s="10"/>
       <c r="G176" s="9"/>
-      <c r="H176" s="8"/>
+      <c r="H176" s="21"/>
       <c r="I176" s="8"/>
     </row>
     <row r="177" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2944,7 +2975,7 @@
       <c r="E177" s="10"/>
       <c r="F177" s="10"/>
       <c r="G177" s="9"/>
-      <c r="H177" s="8"/>
+      <c r="H177" s="21"/>
       <c r="I177" s="8"/>
     </row>
     <row r="178" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2955,7 +2986,7 @@
       <c r="E178" s="10"/>
       <c r="F178" s="10"/>
       <c r="G178" s="9"/>
-      <c r="H178" s="8"/>
+      <c r="H178" s="21"/>
       <c r="I178" s="8"/>
     </row>
     <row r="179" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2966,7 +2997,7 @@
       <c r="E179" s="10"/>
       <c r="F179" s="10"/>
       <c r="G179" s="9"/>
-      <c r="H179" s="8"/>
+      <c r="H179" s="21"/>
       <c r="I179" s="8"/>
     </row>
     <row r="180" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2977,7 +3008,7 @@
       <c r="E180" s="10"/>
       <c r="F180" s="10"/>
       <c r="G180" s="9"/>
-      <c r="H180" s="8"/>
+      <c r="H180" s="21"/>
       <c r="I180" s="8"/>
     </row>
     <row r="181" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2988,7 +3019,7 @@
       <c r="E181" s="10"/>
       <c r="F181" s="10"/>
       <c r="G181" s="9"/>
-      <c r="H181" s="8"/>
+      <c r="H181" s="21"/>
       <c r="I181" s="8"/>
     </row>
     <row r="182" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -2999,7 +3030,7 @@
       <c r="E182" s="10"/>
       <c r="F182" s="10"/>
       <c r="G182" s="9"/>
-      <c r="H182" s="8"/>
+      <c r="H182" s="21"/>
       <c r="I182" s="8"/>
     </row>
     <row r="183" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3010,7 +3041,7 @@
       <c r="E183" s="10"/>
       <c r="F183" s="10"/>
       <c r="G183" s="9"/>
-      <c r="H183" s="8"/>
+      <c r="H183" s="21"/>
       <c r="I183" s="8"/>
     </row>
     <row r="184" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3021,7 +3052,7 @@
       <c r="E184" s="10"/>
       <c r="F184" s="10"/>
       <c r="G184" s="9"/>
-      <c r="H184" s="8"/>
+      <c r="H184" s="21"/>
       <c r="I184" s="8"/>
     </row>
     <row r="185" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3032,7 +3063,7 @@
       <c r="E185" s="10"/>
       <c r="F185" s="10"/>
       <c r="G185" s="9"/>
-      <c r="H185" s="8"/>
+      <c r="H185" s="21"/>
       <c r="I185" s="8"/>
     </row>
     <row r="186" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3043,7 +3074,7 @@
       <c r="E186" s="10"/>
       <c r="F186" s="10"/>
       <c r="G186" s="9"/>
-      <c r="H186" s="8"/>
+      <c r="H186" s="21"/>
       <c r="I186" s="8"/>
     </row>
     <row r="187" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3054,7 +3085,7 @@
       <c r="E187" s="10"/>
       <c r="F187" s="10"/>
       <c r="G187" s="9"/>
-      <c r="H187" s="8"/>
+      <c r="H187" s="21"/>
       <c r="I187" s="8"/>
     </row>
     <row r="188" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3065,7 +3096,7 @@
       <c r="E188" s="10"/>
       <c r="F188" s="10"/>
       <c r="G188" s="9"/>
-      <c r="H188" s="8"/>
+      <c r="H188" s="21"/>
       <c r="I188" s="8"/>
     </row>
     <row r="189" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3076,7 +3107,7 @@
       <c r="E189" s="10"/>
       <c r="F189" s="10"/>
       <c r="G189" s="9"/>
-      <c r="H189" s="8"/>
+      <c r="H189" s="21"/>
       <c r="I189" s="8"/>
     </row>
     <row r="190" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3087,7 +3118,7 @@
       <c r="E190" s="10"/>
       <c r="F190" s="10"/>
       <c r="G190" s="9"/>
-      <c r="H190" s="8"/>
+      <c r="H190" s="21"/>
       <c r="I190" s="8"/>
     </row>
     <row r="191" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3098,7 +3129,7 @@
       <c r="E191" s="10"/>
       <c r="F191" s="10"/>
       <c r="G191" s="9"/>
-      <c r="H191" s="8"/>
+      <c r="H191" s="21"/>
       <c r="I191" s="8"/>
     </row>
     <row r="192" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3109,7 +3140,7 @@
       <c r="E192" s="10"/>
       <c r="F192" s="10"/>
       <c r="G192" s="9"/>
-      <c r="H192" s="8"/>
+      <c r="H192" s="21"/>
       <c r="I192" s="8"/>
     </row>
     <row r="193" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3120,7 +3151,7 @@
       <c r="E193" s="10"/>
       <c r="F193" s="10"/>
       <c r="G193" s="9"/>
-      <c r="H193" s="8"/>
+      <c r="H193" s="21"/>
       <c r="I193" s="8"/>
     </row>
     <row r="194" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3131,7 +3162,7 @@
       <c r="E194" s="10"/>
       <c r="F194" s="10"/>
       <c r="G194" s="9"/>
-      <c r="H194" s="8"/>
+      <c r="H194" s="21"/>
       <c r="I194" s="8"/>
     </row>
     <row r="195" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3142,7 +3173,7 @@
       <c r="E195" s="10"/>
       <c r="F195" s="10"/>
       <c r="G195" s="9"/>
-      <c r="H195" s="8"/>
+      <c r="H195" s="21"/>
       <c r="I195" s="8"/>
     </row>
     <row r="196" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3153,7 +3184,7 @@
       <c r="E196" s="10"/>
       <c r="F196" s="10"/>
       <c r="G196" s="9"/>
-      <c r="H196" s="8"/>
+      <c r="H196" s="21"/>
       <c r="I196" s="8"/>
     </row>
     <row r="197" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3164,7 +3195,7 @@
       <c r="E197" s="10"/>
       <c r="F197" s="10"/>
       <c r="G197" s="9"/>
-      <c r="H197" s="8"/>
+      <c r="H197" s="21"/>
       <c r="I197" s="8"/>
     </row>
     <row r="198" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3175,7 +3206,7 @@
       <c r="E198" s="10"/>
       <c r="F198" s="10"/>
       <c r="G198" s="9"/>
-      <c r="H198" s="8"/>
+      <c r="H198" s="21"/>
       <c r="I198" s="8"/>
     </row>
     <row r="199" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3186,7 +3217,7 @@
       <c r="E199" s="10"/>
       <c r="F199" s="10"/>
       <c r="G199" s="9"/>
-      <c r="H199" s="8"/>
+      <c r="H199" s="21"/>
       <c r="I199" s="8"/>
     </row>
     <row r="200" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3197,7 +3228,7 @@
       <c r="E200" s="10"/>
       <c r="F200" s="10"/>
       <c r="G200" s="9"/>
-      <c r="H200" s="8"/>
+      <c r="H200" s="21"/>
       <c r="I200" s="8"/>
     </row>
     <row r="201" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3208,7 +3239,7 @@
       <c r="E201" s="10"/>
       <c r="F201" s="10"/>
       <c r="G201" s="9"/>
-      <c r="H201" s="8"/>
+      <c r="H201" s="21"/>
       <c r="I201" s="8"/>
     </row>
     <row r="202" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3219,7 +3250,7 @@
       <c r="E202" s="10"/>
       <c r="F202" s="10"/>
       <c r="G202" s="9"/>
-      <c r="H202" s="8"/>
+      <c r="H202" s="21"/>
       <c r="I202" s="8"/>
     </row>
     <row r="203" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3230,7 +3261,7 @@
       <c r="E203" s="10"/>
       <c r="F203" s="10"/>
       <c r="G203" s="9"/>
-      <c r="H203" s="8"/>
+      <c r="H203" s="21"/>
       <c r="I203" s="8"/>
     </row>
     <row r="204" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3241,7 +3272,7 @@
       <c r="E204" s="10"/>
       <c r="F204" s="10"/>
       <c r="G204" s="9"/>
-      <c r="H204" s="8"/>
+      <c r="H204" s="21"/>
       <c r="I204" s="8"/>
     </row>
     <row r="205" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3252,7 +3283,7 @@
       <c r="E205" s="10"/>
       <c r="F205" s="10"/>
       <c r="G205" s="9"/>
-      <c r="H205" s="8"/>
+      <c r="H205" s="21"/>
       <c r="I205" s="8"/>
     </row>
     <row r="206" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3263,7 +3294,7 @@
       <c r="E206" s="10"/>
       <c r="F206" s="10"/>
       <c r="G206" s="9"/>
-      <c r="H206" s="8"/>
+      <c r="H206" s="21"/>
       <c r="I206" s="8"/>
     </row>
     <row r="207" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3274,7 +3305,7 @@
       <c r="E207" s="10"/>
       <c r="F207" s="10"/>
       <c r="G207" s="9"/>
-      <c r="H207" s="8"/>
+      <c r="H207" s="21"/>
       <c r="I207" s="8"/>
     </row>
     <row r="208" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3285,7 +3316,7 @@
       <c r="E208" s="10"/>
       <c r="F208" s="10"/>
       <c r="G208" s="9"/>
-      <c r="H208" s="8"/>
+      <c r="H208" s="21"/>
       <c r="I208" s="8"/>
     </row>
     <row r="209" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3296,7 +3327,7 @@
       <c r="E209" s="10"/>
       <c r="F209" s="10"/>
       <c r="G209" s="9"/>
-      <c r="H209" s="8"/>
+      <c r="H209" s="21"/>
       <c r="I209" s="8"/>
     </row>
     <row r="210" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3307,7 +3338,7 @@
       <c r="E210" s="10"/>
       <c r="F210" s="10"/>
       <c r="G210" s="9"/>
-      <c r="H210" s="8"/>
+      <c r="H210" s="21"/>
       <c r="I210" s="8"/>
     </row>
     <row r="211" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3318,7 +3349,7 @@
       <c r="E211" s="10"/>
       <c r="F211" s="10"/>
       <c r="G211" s="9"/>
-      <c r="H211" s="8"/>
+      <c r="H211" s="21"/>
       <c r="I211" s="8"/>
     </row>
     <row r="212" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3329,7 +3360,7 @@
       <c r="E212" s="10"/>
       <c r="F212" s="10"/>
       <c r="G212" s="9"/>
-      <c r="H212" s="8"/>
+      <c r="H212" s="21"/>
       <c r="I212" s="8"/>
     </row>
     <row r="213" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3340,7 +3371,7 @@
       <c r="E213" s="10"/>
       <c r="F213" s="10"/>
       <c r="G213" s="9"/>
-      <c r="H213" s="8"/>
+      <c r="H213" s="21"/>
       <c r="I213" s="8"/>
     </row>
     <row r="214" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3351,7 +3382,7 @@
       <c r="E214" s="10"/>
       <c r="F214" s="10"/>
       <c r="G214" s="9"/>
-      <c r="H214" s="8"/>
+      <c r="H214" s="21"/>
       <c r="I214" s="8"/>
     </row>
     <row r="215" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3362,7 +3393,7 @@
       <c r="E215" s="10"/>
       <c r="F215" s="10"/>
       <c r="G215" s="9"/>
-      <c r="H215" s="8"/>
+      <c r="H215" s="21"/>
       <c r="I215" s="8"/>
     </row>
     <row r="216" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3373,7 +3404,7 @@
       <c r="E216" s="10"/>
       <c r="F216" s="10"/>
       <c r="G216" s="9"/>
-      <c r="H216" s="8"/>
+      <c r="H216" s="21"/>
       <c r="I216" s="8"/>
     </row>
     <row r="217" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3384,7 +3415,7 @@
       <c r="E217" s="10"/>
       <c r="F217" s="10"/>
       <c r="G217" s="9"/>
-      <c r="H217" s="8"/>
+      <c r="H217" s="21"/>
       <c r="I217" s="8"/>
     </row>
     <row r="218" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3395,7 +3426,7 @@
       <c r="E218" s="10"/>
       <c r="F218" s="10"/>
       <c r="G218" s="9"/>
-      <c r="H218" s="8"/>
+      <c r="H218" s="21"/>
       <c r="I218" s="8"/>
     </row>
     <row r="219" spans="1:9" ht="13" x14ac:dyDescent="0.15">
@@ -3406,7 +3437,7 @@
       <c r="E219" s="10"/>
       <c r="F219" s="10"/>
       <c r="G219" s="9"/>
-      <c r="H219" s="8"/>
+      <c r="H219" s="21"/>
       <c r="I219" s="8"/>
     </row>
     <row r="220" spans="1:9" ht="13" x14ac:dyDescent="0.15">

--- a/docs/StatusTracker.xlsx
+++ b/docs/StatusTracker.xlsx
@@ -1,12 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaushikyadala/Documents/IIIT/Fourth_Sem/DASS/project-monorepo-team-35/docs/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71E9ECB-7B51-1C4B-8DC1-B222BD3B5C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="200" yWindow="1000" windowWidth="35600" windowHeight="22180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -202,39 +224,39 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -244,7 +266,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -272,96 +294,93 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -551,40 +570,43 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="49.63"/>
-    <col customWidth="1" min="2" max="2" width="73.5"/>
-    <col customWidth="1" min="3" max="3" width="16.25"/>
-    <col customWidth="1" min="4" max="4" width="20.13"/>
-    <col customWidth="1" min="5" max="6" width="12.63"/>
-    <col customWidth="1" min="7" max="7" width="80.38"/>
-    <col customWidth="1" min="8" max="8" width="14.63"/>
-    <col customWidth="1" min="9" max="9" width="18.13"/>
+    <col min="1" max="1" width="49.6640625" customWidth="1"/>
+    <col min="2" max="2" width="73.5" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" customWidth="1"/>
+    <col min="5" max="6" width="12.6640625" customWidth="1"/>
+    <col min="7" max="7" width="80.33203125" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="9" max="9" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="H1" s="3">
         <f>D:D-E:E</f>
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -593,7 +615,7 @@
       </c>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -602,7 +624,7 @@
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" ht="16.5" customHeight="1">
+    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -631,7 +653,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
@@ -644,7 +666,7 @@
       <c r="H5" s="6"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
@@ -665,12 +687,12 @@
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="6">
-        <f t="shared" ref="H6:H23" si="1">D:D-E:E</f>
+        <f t="shared" ref="H6:H23" si="0">D:D-E:E</f>
         <v>0.1</v>
       </c>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
@@ -681,7 +703,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="11">
         <v>0.5</v>
@@ -693,12 +715,12 @@
         <v>21</v>
       </c>
       <c r="H7" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10" t="s">
         <v>22</v>
       </c>
@@ -709,7 +731,7 @@
         <v>24</v>
       </c>
       <c r="D8" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="11">
         <v>0.75</v>
@@ -719,12 +741,12 @@
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10" t="s">
         <v>25</v>
       </c>
@@ -738,19 +760,19 @@
         <v>1.5</v>
       </c>
       <c r="E9" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>18</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10" t="s">
         <v>27</v>
       </c>
@@ -771,12 +793,12 @@
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10" t="s">
         <v>29</v>
       </c>
@@ -787,7 +809,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="11">
         <v>0.5</v>
@@ -799,12 +821,12 @@
         <v>30</v>
       </c>
       <c r="H11" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
         <v>31</v>
       </c>
@@ -815,12 +837,12 @@
       <c r="F12" s="8"/>
       <c r="G12" s="7"/>
       <c r="H12" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10" t="s">
         <v>19</v>
       </c>
@@ -841,12 +863,12 @@
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="6">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
+        <f t="shared" si="0"/>
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10" t="s">
         <v>27</v>
       </c>
@@ -867,12 +889,12 @@
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="13" t="s">
         <v>33</v>
       </c>
@@ -883,11 +905,11 @@
         <v>26</v>
       </c>
       <c r="H15" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10" t="s">
         <v>35</v>
       </c>
@@ -908,12 +930,12 @@
       </c>
       <c r="G16" s="10"/>
       <c r="H16" s="6">
-        <f t="shared" si="1"/>
-        <v>0.05</v>
+        <f t="shared" si="0"/>
+        <v>4.9999999999999989E-2</v>
       </c>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10" t="s">
         <v>29</v>
       </c>
@@ -936,12 +958,12 @@
         <v>36</v>
       </c>
       <c r="H17" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
         <v>37</v>
       </c>
@@ -952,12 +974,12 @@
       <c r="F18" s="8"/>
       <c r="G18" s="7"/>
       <c r="H18" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10" t="s">
         <v>19</v>
       </c>
@@ -968,7 +990,7 @@
         <v>32</v>
       </c>
       <c r="D19" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="11">
         <v>1.25</v>
@@ -980,12 +1002,12 @@
         <v>38</v>
       </c>
       <c r="H19" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>-0.25</v>
       </c>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10" t="s">
         <v>27</v>
       </c>
@@ -1006,12 +1028,12 @@
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="10" t="s">
         <v>29</v>
       </c>
@@ -1024,18 +1046,20 @@
       <c r="D21" s="11">
         <v>0.75</v>
       </c>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11" t="s">
-        <v>39</v>
+      <c r="E21" s="11">
+        <v>1</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="6">
-        <f t="shared" si="1"/>
-        <v>0.75</v>
+        <f t="shared" si="0"/>
+        <v>-0.25</v>
       </c>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10" t="s">
         <v>40</v>
       </c>
@@ -1046,7 +1070,7 @@
         <v>28</v>
       </c>
       <c r="D22" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="11">
         <v>1.75</v>
@@ -1056,12 +1080,12 @@
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10" t="s">
         <v>41</v>
       </c>
@@ -1072,20 +1096,20 @@
         <v>24</v>
       </c>
       <c r="D23" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="11">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>18</v>
       </c>
       <c r="H23" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
         <v>42</v>
       </c>
@@ -1098,7 +1122,7 @@
       <c r="H24" s="6"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10" t="s">
         <v>43</v>
       </c>
@@ -1113,7 +1137,7 @@
       <c r="H25" s="6"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="11" t="s">
         <v>44</v>
       </c>
@@ -1122,20 +1146,20 @@
         <v>17</v>
       </c>
       <c r="D26" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="E26" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="F26" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="11">
+        <v>1</v>
+      </c>
+      <c r="F26" s="14" t="s">
         <v>18</v>
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="6">
-        <f t="shared" ref="H26:H29" si="2">D:D-E:E</f>
+        <f t="shared" ref="H26:H29" si="1">D:D-E:E</f>
         <v>0</v>
       </c>
-      <c r="I26" s="16"/>
+      <c r="I26" s="15"/>
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
       <c r="L26" s="13"/>
@@ -1154,7 +1178,7 @@
       <c r="Y26" s="13"/>
       <c r="Z26" s="13"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="11" t="s">
         <v>45</v>
       </c>
@@ -1163,20 +1187,20 @@
         <v>28</v>
       </c>
       <c r="D27" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="E27" s="17">
+        <v>1</v>
+      </c>
+      <c r="E27" s="13">
         <v>1.25</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F27" s="14" t="s">
         <v>18</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-0.25</v>
       </c>
-      <c r="I27" s="16"/>
+      <c r="I27" s="15"/>
       <c r="J27" s="13"/>
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
@@ -1195,7 +1219,7 @@
       <c r="Y27" s="13"/>
       <c r="Z27" s="13"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="11" t="s">
         <v>46</v>
       </c>
@@ -1204,20 +1228,20 @@
         <v>20</v>
       </c>
       <c r="D28" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="E28" s="17">
+        <v>1</v>
+      </c>
+      <c r="E28" s="13">
         <v>1.5</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="F28" s="14" t="s">
         <v>18</v>
       </c>
       <c r="G28" s="13"/>
       <c r="H28" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-0.5</v>
       </c>
-      <c r="I28" s="16"/>
+      <c r="I28" s="15"/>
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
@@ -1236,7 +1260,7 @@
       <c r="Y28" s="13"/>
       <c r="Z28" s="13"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="11" t="s">
         <v>47</v>
       </c>
@@ -1245,7 +1269,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="13">
         <v>1.5</v>
@@ -1255,10 +1279,10 @@
       </c>
       <c r="G29" s="13"/>
       <c r="H29" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-0.5</v>
       </c>
-      <c r="I29" s="16"/>
+      <c r="I29" s="15"/>
       <c r="J29" s="13"/>
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
@@ -1277,7 +1301,7 @@
       <c r="Y29" s="13"/>
       <c r="Z29" s="13"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="11" t="s">
         <v>48</v>
       </c>
@@ -1286,7 +1310,7 @@
         <v>26</v>
       </c>
       <c r="D30" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="13"/>
       <c r="F30" s="11" t="s">
@@ -1296,7 +1320,7 @@
       <c r="H30" s="6"/>
       <c r="I30" s="9"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="11" t="s">
         <v>49</v>
       </c>
@@ -1317,11 +1341,11 @@
         <v>50</v>
       </c>
       <c r="H31" s="6">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10" t="s">
         <v>51</v>
       </c>
@@ -1335,19 +1359,19 @@
         <v>1.5</v>
       </c>
       <c r="E32" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>39</v>
+        <v>1</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="G32" s="10"/>
       <c r="H32" s="6">
-        <f t="shared" ref="H32:H33" si="3">D:D-E:E</f>
+        <f t="shared" ref="H32:H33" si="2">D:D-E:E</f>
         <v>0.5</v>
       </c>
       <c r="I32" s="9"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10" t="s">
         <v>53</v>
       </c>
@@ -1368,181 +1392,181 @@
       </c>
       <c r="G33" s="10"/>
       <c r="H33" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-0.25</v>
       </c>
       <c r="I33" s="9"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="18" t="s">
+    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="19"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="17"/>
       <c r="H34" s="6"/>
       <c r="I34" s="9"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="21" t="s">
+    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="11">
         <v>1.5</v>
       </c>
-      <c r="E35" s="14">
-        <v>2.0</v>
-      </c>
-      <c r="F35" s="15" t="s">
+      <c r="E35" s="11">
+        <v>2</v>
+      </c>
+      <c r="F35" s="14" t="s">
         <v>18</v>
       </c>
       <c r="G35" s="10"/>
       <c r="H35" s="6">
-        <f t="shared" ref="H35:H40" si="4">D:D-E:E</f>
+        <f t="shared" ref="H35:H40" si="3">D:D-E:E</f>
         <v>-0.5</v>
       </c>
       <c r="I35" s="9"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="21" t="s">
+    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="11">
         <v>0.5</v>
       </c>
-      <c r="E36" s="14">
+      <c r="E36" s="11">
         <v>0.6</v>
       </c>
-      <c r="F36" s="15" t="s">
+      <c r="F36" s="14" t="s">
         <v>18</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="6">
-        <f t="shared" si="4"/>
-        <v>-0.1</v>
+        <f t="shared" si="3"/>
+        <v>-9.9999999999999978E-2</v>
       </c>
       <c r="I36" s="9"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="21" t="s">
+    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="11">
         <v>0.5</v>
       </c>
-      <c r="E37" s="14">
+      <c r="E37" s="11">
         <v>0.7</v>
       </c>
-      <c r="F37" s="15" t="s">
+      <c r="F37" s="14" t="s">
         <v>18</v>
       </c>
       <c r="G37" s="10"/>
       <c r="H37" s="6">
-        <f t="shared" si="4"/>
-        <v>-0.2</v>
+        <f t="shared" si="3"/>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="I37" s="9"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="21" t="s">
+    <row r="38" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="11">
         <v>0.5</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E38" s="11">
         <v>0.5</v>
       </c>
-      <c r="F38" s="15" t="s">
+      <c r="F38" s="14" t="s">
         <v>18</v>
       </c>
       <c r="G38" s="10"/>
       <c r="H38" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I38" s="9"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="21" t="s">
+    <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="11">
         <v>1.5</v>
       </c>
-      <c r="E39" s="14">
-        <v>2.0</v>
-      </c>
-      <c r="F39" s="15" t="s">
+      <c r="E39" s="11">
+        <v>2</v>
+      </c>
+      <c r="F39" s="14" t="s">
         <v>18</v>
       </c>
       <c r="G39" s="10"/>
       <c r="H39" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.5</v>
       </c>
       <c r="I39" s="9"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="21" t="s">
+    <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="11">
         <v>0.5</v>
       </c>
-      <c r="E40" s="14">
+      <c r="E40" s="11">
         <v>0.4</v>
       </c>
-      <c r="F40" s="15" t="s">
+      <c r="F40" s="14" t="s">
         <v>18</v>
       </c>
       <c r="G40" s="10"/>
       <c r="H40" s="6">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
+        <f t="shared" si="3"/>
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="I40" s="9"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="11"/>
@@ -1553,7 +1577,7 @@
       <c r="H41" s="6"/>
       <c r="I41" s="9"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="11"/>
@@ -1564,7 +1588,7 @@
       <c r="H42" s="6"/>
       <c r="I42" s="9"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="C43" s="11"/>
@@ -1575,7 +1599,7 @@
       <c r="H43" s="6"/>
       <c r="I43" s="9"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
@@ -1586,7 +1610,7 @@
       <c r="H44" s="6"/>
       <c r="I44" s="9"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="10"/>
       <c r="B45" s="10"/>
       <c r="C45" s="11"/>
@@ -1597,7 +1621,7 @@
       <c r="H45" s="6"/>
       <c r="I45" s="9"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="10"/>
       <c r="C46" s="11"/>
@@ -1608,7 +1632,7 @@
       <c r="H46" s="6"/>
       <c r="I46" s="9"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="10"/>
       <c r="C47" s="11"/>
@@ -1619,7 +1643,7 @@
       <c r="H47" s="6"/>
       <c r="I47" s="9"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
@@ -1630,7 +1654,7 @@
       <c r="H48" s="6"/>
       <c r="I48" s="9"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
@@ -1641,7 +1665,7 @@
       <c r="H49" s="6"/>
       <c r="I49" s="9"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="11"/>
@@ -1652,7 +1676,7 @@
       <c r="H50" s="6"/>
       <c r="I50" s="9"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="11"/>
@@ -1663,7 +1687,7 @@
       <c r="H51" s="6"/>
       <c r="I51" s="9"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="11"/>
@@ -1674,7 +1698,7 @@
       <c r="H52" s="6"/>
       <c r="I52" s="9"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="11"/>
@@ -1685,7 +1709,7 @@
       <c r="H53" s="6"/>
       <c r="I53" s="9"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
@@ -1696,7 +1720,7 @@
       <c r="H54" s="6"/>
       <c r="I54" s="9"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="11"/>
@@ -1707,7 +1731,7 @@
       <c r="H55" s="6"/>
       <c r="I55" s="9"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="11"/>
@@ -1718,7 +1742,7 @@
       <c r="H56" s="6"/>
       <c r="I56" s="9"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11"/>
@@ -1729,7 +1753,7 @@
       <c r="H57" s="6"/>
       <c r="I57" s="9"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="10"/>
       <c r="C58" s="11"/>
@@ -1740,7 +1764,7 @@
       <c r="H58" s="6"/>
       <c r="I58" s="9"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="10"/>
       <c r="C59" s="11"/>
@@ -1751,7 +1775,7 @@
       <c r="H59" s="6"/>
       <c r="I59" s="9"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="10"/>
       <c r="C60" s="11"/>
@@ -1762,7 +1786,7 @@
       <c r="H60" s="6"/>
       <c r="I60" s="9"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="10"/>
       <c r="C61" s="11"/>
@@ -1773,7 +1797,7 @@
       <c r="H61" s="6"/>
       <c r="I61" s="9"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="10"/>
       <c r="C62" s="11"/>
@@ -1784,7 +1808,7 @@
       <c r="H62" s="6"/>
       <c r="I62" s="9"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="10"/>
       <c r="C63" s="11"/>
@@ -1795,7 +1819,7 @@
       <c r="H63" s="6"/>
       <c r="I63" s="9"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="B64" s="10"/>
       <c r="C64" s="11"/>
@@ -1806,7 +1830,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="9"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="10"/>
       <c r="C65" s="11"/>
@@ -1817,7 +1841,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="9"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="10"/>
       <c r="C66" s="11"/>
@@ -1828,7 +1852,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="9"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="10"/>
       <c r="C67" s="11"/>
@@ -1839,7 +1863,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="9"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="10"/>
       <c r="C68" s="11"/>
@@ -1850,7 +1874,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="9"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="10"/>
       <c r="C69" s="11"/>
@@ -1861,7 +1885,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="9"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
       <c r="B70" s="10"/>
       <c r="C70" s="11"/>
@@ -1872,7 +1896,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="9"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="10"/>
       <c r="B71" s="10"/>
       <c r="C71" s="11"/>
@@ -1883,7 +1907,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="9"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="10"/>
       <c r="C72" s="11"/>
@@ -1894,7 +1918,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="9"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="10"/>
       <c r="C73" s="11"/>
@@ -1905,7 +1929,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="9"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="10"/>
       <c r="C74" s="11"/>
@@ -1916,7 +1940,7 @@
       <c r="H74" s="6"/>
       <c r="I74" s="9"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="10"/>
       <c r="C75" s="11"/>
@@ -1927,7 +1951,7 @@
       <c r="H75" s="6"/>
       <c r="I75" s="9"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="10"/>
       <c r="C76" s="11"/>
@@ -1938,7 +1962,7 @@
       <c r="H76" s="6"/>
       <c r="I76" s="9"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="10"/>
       <c r="C77" s="11"/>
@@ -1949,7 +1973,7 @@
       <c r="H77" s="6"/>
       <c r="I77" s="9"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="10"/>
       <c r="C78" s="11"/>
@@ -1960,7 +1984,7 @@
       <c r="H78" s="6"/>
       <c r="I78" s="9"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="10"/>
       <c r="C79" s="11"/>
@@ -1971,7 +1995,7 @@
       <c r="H79" s="6"/>
       <c r="I79" s="9"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="10"/>
       <c r="C80" s="11"/>
@@ -1982,7 +2006,7 @@
       <c r="H80" s="6"/>
       <c r="I80" s="9"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="10"/>
       <c r="C81" s="11"/>
@@ -1993,7 +2017,7 @@
       <c r="H81" s="6"/>
       <c r="I81" s="9"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="10"/>
       <c r="C82" s="11"/>
@@ -2004,7 +2028,7 @@
       <c r="H82" s="6"/>
       <c r="I82" s="9"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="10"/>
       <c r="C83" s="11"/>
@@ -2015,7 +2039,7 @@
       <c r="H83" s="6"/>
       <c r="I83" s="9"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="10"/>
       <c r="C84" s="11"/>
@@ -2026,7 +2050,7 @@
       <c r="H84" s="6"/>
       <c r="I84" s="9"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="10"/>
       <c r="C85" s="11"/>
@@ -2037,7 +2061,7 @@
       <c r="H85" s="6"/>
       <c r="I85" s="9"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="10"/>
       <c r="C86" s="11"/>
@@ -2048,7 +2072,7 @@
       <c r="H86" s="6"/>
       <c r="I86" s="9"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="10"/>
       <c r="C87" s="11"/>
@@ -2059,7 +2083,7 @@
       <c r="H87" s="6"/>
       <c r="I87" s="9"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="B88" s="10"/>
       <c r="C88" s="11"/>
@@ -2070,7 +2094,7 @@
       <c r="H88" s="6"/>
       <c r="I88" s="9"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="10"/>
       <c r="C89" s="11"/>
@@ -2081,7 +2105,7 @@
       <c r="H89" s="6"/>
       <c r="I89" s="9"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="10"/>
       <c r="C90" s="11"/>
@@ -2092,7 +2116,7 @@
       <c r="H90" s="6"/>
       <c r="I90" s="9"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="10"/>
       <c r="C91" s="11"/>
@@ -2103,7 +2127,7 @@
       <c r="H91" s="6"/>
       <c r="I91" s="9"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="10"/>
       <c r="C92" s="11"/>
@@ -2114,7 +2138,7 @@
       <c r="H92" s="6"/>
       <c r="I92" s="9"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="10"/>
       <c r="C93" s="11"/>
@@ -2125,7 +2149,7 @@
       <c r="H93" s="6"/>
       <c r="I93" s="9"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="B94" s="10"/>
       <c r="C94" s="11"/>
@@ -2136,7 +2160,7 @@
       <c r="H94" s="6"/>
       <c r="I94" s="9"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="10"/>
       <c r="C95" s="11"/>
@@ -2147,7 +2171,7 @@
       <c r="H95" s="6"/>
       <c r="I95" s="9"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="10"/>
       <c r="C96" s="11"/>
@@ -2158,7 +2182,7 @@
       <c r="H96" s="6"/>
       <c r="I96" s="9"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="10"/>
       <c r="C97" s="11"/>
@@ -2169,7 +2193,7 @@
       <c r="H97" s="6"/>
       <c r="I97" s="9"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
       <c r="B98" s="10"/>
       <c r="C98" s="11"/>
@@ -2180,7 +2204,7 @@
       <c r="H98" s="6"/>
       <c r="I98" s="9"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="10"/>
       <c r="B99" s="10"/>
       <c r="C99" s="11"/>
@@ -2191,7 +2215,7 @@
       <c r="H99" s="6"/>
       <c r="I99" s="9"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="10"/>
       <c r="C100" s="11"/>
@@ -2202,7 +2226,7 @@
       <c r="H100" s="6"/>
       <c r="I100" s="9"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="10"/>
       <c r="C101" s="11"/>
@@ -2213,7 +2237,7 @@
       <c r="H101" s="6"/>
       <c r="I101" s="9"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="10"/>
       <c r="C102" s="11"/>
@@ -2224,7 +2248,7 @@
       <c r="H102" s="6"/>
       <c r="I102" s="9"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="10"/>
       <c r="C103" s="11"/>
@@ -2235,7 +2259,7 @@
       <c r="H103" s="6"/>
       <c r="I103" s="9"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="10"/>
       <c r="C104" s="11"/>
@@ -2246,7 +2270,7 @@
       <c r="H104" s="6"/>
       <c r="I104" s="9"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="10"/>
       <c r="C105" s="11"/>
@@ -2257,7 +2281,7 @@
       <c r="H105" s="6"/>
       <c r="I105" s="9"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="B106" s="10"/>
       <c r="C106" s="11"/>
@@ -2268,7 +2292,7 @@
       <c r="H106" s="6"/>
       <c r="I106" s="9"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="10"/>
       <c r="C107" s="11"/>
@@ -2279,7 +2303,7 @@
       <c r="H107" s="6"/>
       <c r="I107" s="9"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="10"/>
       <c r="C108" s="11"/>
@@ -2290,7 +2314,7 @@
       <c r="H108" s="6"/>
       <c r="I108" s="9"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="10"/>
       <c r="C109" s="11"/>
@@ -2301,7 +2325,7 @@
       <c r="H109" s="6"/>
       <c r="I109" s="9"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="10"/>
       <c r="C110" s="11"/>
@@ -2312,7 +2336,7 @@
       <c r="H110" s="6"/>
       <c r="I110" s="9"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="B111" s="10"/>
       <c r="C111" s="11"/>
@@ -2323,7 +2347,7 @@
       <c r="H111" s="6"/>
       <c r="I111" s="9"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="10"/>
       <c r="C112" s="11"/>
@@ -2334,7 +2358,7 @@
       <c r="H112" s="6"/>
       <c r="I112" s="9"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="10"/>
       <c r="C113" s="11"/>
@@ -2345,7 +2369,7 @@
       <c r="H113" s="6"/>
       <c r="I113" s="9"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="10"/>
       <c r="C114" s="11"/>
@@ -2356,7 +2380,7 @@
       <c r="H114" s="6"/>
       <c r="I114" s="9"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="B115" s="10"/>
       <c r="C115" s="11"/>
@@ -2367,7 +2391,7 @@
       <c r="H115" s="6"/>
       <c r="I115" s="9"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="10"/>
       <c r="C116" s="11"/>
@@ -2378,7 +2402,7 @@
       <c r="H116" s="6"/>
       <c r="I116" s="9"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="10"/>
       <c r="C117" s="11"/>
@@ -2389,7 +2413,7 @@
       <c r="H117" s="6"/>
       <c r="I117" s="9"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="10"/>
       <c r="B118" s="10"/>
       <c r="C118" s="11"/>
@@ -2400,7 +2424,7 @@
       <c r="H118" s="6"/>
       <c r="I118" s="9"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="10"/>
       <c r="B119" s="10"/>
       <c r="C119" s="11"/>
@@ -2411,7 +2435,7 @@
       <c r="H119" s="6"/>
       <c r="I119" s="9"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="10"/>
       <c r="C120" s="11"/>
@@ -2422,7 +2446,7 @@
       <c r="H120" s="6"/>
       <c r="I120" s="9"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="10"/>
       <c r="C121" s="11"/>
@@ -2433,7 +2457,7 @@
       <c r="H121" s="6"/>
       <c r="I121" s="9"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="10"/>
       <c r="B122" s="10"/>
       <c r="C122" s="11"/>
@@ -2444,7 +2468,7 @@
       <c r="H122" s="6"/>
       <c r="I122" s="9"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="10"/>
       <c r="C123" s="11"/>
@@ -2455,7 +2479,7 @@
       <c r="H123" s="6"/>
       <c r="I123" s="9"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="10"/>
       <c r="C124" s="11"/>
@@ -2466,7 +2490,7 @@
       <c r="H124" s="6"/>
       <c r="I124" s="9"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="10"/>
       <c r="C125" s="11"/>
@@ -2477,7 +2501,7 @@
       <c r="H125" s="6"/>
       <c r="I125" s="9"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="10"/>
       <c r="B126" s="10"/>
       <c r="C126" s="11"/>
@@ -2488,7 +2512,7 @@
       <c r="H126" s="6"/>
       <c r="I126" s="9"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="10"/>
       <c r="B127" s="10"/>
       <c r="C127" s="11"/>
@@ -2499,7 +2523,7 @@
       <c r="H127" s="6"/>
       <c r="I127" s="9"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="10"/>
       <c r="B128" s="10"/>
       <c r="C128" s="11"/>
@@ -2510,7 +2534,7 @@
       <c r="H128" s="6"/>
       <c r="I128" s="9"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="10"/>
       <c r="B129" s="10"/>
       <c r="C129" s="11"/>
@@ -2521,7 +2545,7 @@
       <c r="H129" s="6"/>
       <c r="I129" s="9"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="10"/>
       <c r="B130" s="10"/>
       <c r="C130" s="11"/>
@@ -2532,7 +2556,7 @@
       <c r="H130" s="6"/>
       <c r="I130" s="9"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="10"/>
       <c r="B131" s="10"/>
       <c r="C131" s="11"/>
@@ -2543,7 +2567,7 @@
       <c r="H131" s="6"/>
       <c r="I131" s="9"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="10"/>
       <c r="B132" s="10"/>
       <c r="C132" s="11"/>
@@ -2554,7 +2578,7 @@
       <c r="H132" s="6"/>
       <c r="I132" s="9"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="10"/>
       <c r="B133" s="10"/>
       <c r="C133" s="11"/>
@@ -2565,7 +2589,7 @@
       <c r="H133" s="6"/>
       <c r="I133" s="9"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="10"/>
       <c r="B134" s="10"/>
       <c r="C134" s="11"/>
@@ -2576,7 +2600,7 @@
       <c r="H134" s="6"/>
       <c r="I134" s="9"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="10"/>
       <c r="B135" s="10"/>
       <c r="C135" s="11"/>
@@ -2587,7 +2611,7 @@
       <c r="H135" s="6"/>
       <c r="I135" s="9"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="10"/>
       <c r="B136" s="10"/>
       <c r="C136" s="11"/>
@@ -2598,7 +2622,7 @@
       <c r="H136" s="6"/>
       <c r="I136" s="9"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="10"/>
       <c r="B137" s="10"/>
       <c r="C137" s="11"/>
@@ -2609,7 +2633,7 @@
       <c r="H137" s="6"/>
       <c r="I137" s="9"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="10"/>
       <c r="B138" s="10"/>
       <c r="C138" s="11"/>
@@ -2620,7 +2644,7 @@
       <c r="H138" s="6"/>
       <c r="I138" s="9"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="10"/>
       <c r="B139" s="10"/>
       <c r="C139" s="11"/>
@@ -2631,7 +2655,7 @@
       <c r="H139" s="6"/>
       <c r="I139" s="9"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="10"/>
       <c r="B140" s="10"/>
       <c r="C140" s="11"/>
@@ -2642,7 +2666,7 @@
       <c r="H140" s="6"/>
       <c r="I140" s="9"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="10"/>
       <c r="B141" s="10"/>
       <c r="C141" s="11"/>
@@ -2653,7 +2677,7 @@
       <c r="H141" s="6"/>
       <c r="I141" s="9"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="10"/>
       <c r="B142" s="10"/>
       <c r="C142" s="11"/>
@@ -2664,7 +2688,7 @@
       <c r="H142" s="6"/>
       <c r="I142" s="9"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="10"/>
       <c r="B143" s="10"/>
       <c r="C143" s="11"/>
@@ -2675,7 +2699,7 @@
       <c r="H143" s="6"/>
       <c r="I143" s="9"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="10"/>
       <c r="B144" s="10"/>
       <c r="C144" s="11"/>
@@ -2686,7 +2710,7 @@
       <c r="H144" s="6"/>
       <c r="I144" s="9"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="11"/>
@@ -2697,7 +2721,7 @@
       <c r="H145" s="6"/>
       <c r="I145" s="9"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
       <c r="C146" s="11"/>
@@ -2708,7 +2732,7 @@
       <c r="H146" s="6"/>
       <c r="I146" s="9"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
       <c r="C147" s="11"/>
@@ -2719,7 +2743,7 @@
       <c r="H147" s="6"/>
       <c r="I147" s="9"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="10"/>
       <c r="B148" s="10"/>
       <c r="C148" s="11"/>
@@ -2730,7 +2754,7 @@
       <c r="H148" s="6"/>
       <c r="I148" s="9"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="10"/>
       <c r="B149" s="10"/>
       <c r="C149" s="11"/>
@@ -2741,7 +2765,7 @@
       <c r="H149" s="6"/>
       <c r="I149" s="9"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="10"/>
       <c r="B150" s="10"/>
       <c r="C150" s="11"/>
@@ -2752,7 +2776,7 @@
       <c r="H150" s="6"/>
       <c r="I150" s="9"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="10"/>
       <c r="B151" s="10"/>
       <c r="C151" s="11"/>
@@ -2763,7 +2787,7 @@
       <c r="H151" s="6"/>
       <c r="I151" s="9"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="10"/>
       <c r="B152" s="10"/>
       <c r="C152" s="11"/>
@@ -2774,7 +2798,7 @@
       <c r="H152" s="6"/>
       <c r="I152" s="9"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="10"/>
       <c r="B153" s="10"/>
       <c r="C153" s="11"/>
@@ -2785,7 +2809,7 @@
       <c r="H153" s="6"/>
       <c r="I153" s="9"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="10"/>
       <c r="B154" s="10"/>
       <c r="C154" s="11"/>
@@ -2796,7 +2820,7 @@
       <c r="H154" s="6"/>
       <c r="I154" s="9"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="10"/>
       <c r="B155" s="10"/>
       <c r="C155" s="11"/>
@@ -2807,7 +2831,7 @@
       <c r="H155" s="6"/>
       <c r="I155" s="9"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="10"/>
       <c r="B156" s="10"/>
       <c r="C156" s="11"/>
@@ -2818,7 +2842,7 @@
       <c r="H156" s="6"/>
       <c r="I156" s="9"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="10"/>
       <c r="B157" s="10"/>
       <c r="C157" s="11"/>
@@ -2829,7 +2853,7 @@
       <c r="H157" s="6"/>
       <c r="I157" s="9"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="10"/>
       <c r="B158" s="10"/>
       <c r="C158" s="11"/>
@@ -2840,7 +2864,7 @@
       <c r="H158" s="6"/>
       <c r="I158" s="9"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="10"/>
       <c r="B159" s="10"/>
       <c r="C159" s="11"/>
@@ -2851,7 +2875,7 @@
       <c r="H159" s="6"/>
       <c r="I159" s="9"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="10"/>
       <c r="B160" s="10"/>
       <c r="C160" s="11"/>
@@ -2862,7 +2886,7 @@
       <c r="H160" s="6"/>
       <c r="I160" s="9"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="10"/>
       <c r="B161" s="10"/>
       <c r="C161" s="11"/>
@@ -2873,7 +2897,7 @@
       <c r="H161" s="6"/>
       <c r="I161" s="9"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="10"/>
       <c r="B162" s="10"/>
       <c r="C162" s="11"/>
@@ -2884,7 +2908,7 @@
       <c r="H162" s="6"/>
       <c r="I162" s="9"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="10"/>
       <c r="B163" s="10"/>
       <c r="C163" s="11"/>
@@ -2895,7 +2919,7 @@
       <c r="H163" s="6"/>
       <c r="I163" s="9"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="10"/>
       <c r="B164" s="10"/>
       <c r="C164" s="11"/>
@@ -2906,7 +2930,7 @@
       <c r="H164" s="6"/>
       <c r="I164" s="9"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="10"/>
       <c r="B165" s="10"/>
       <c r="C165" s="11"/>
@@ -2917,7 +2941,7 @@
       <c r="H165" s="6"/>
       <c r="I165" s="9"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="10"/>
       <c r="B166" s="10"/>
       <c r="C166" s="11"/>
@@ -2928,7 +2952,7 @@
       <c r="H166" s="6"/>
       <c r="I166" s="9"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="10"/>
       <c r="B167" s="10"/>
       <c r="C167" s="11"/>
@@ -2939,7 +2963,7 @@
       <c r="H167" s="6"/>
       <c r="I167" s="9"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="10"/>
       <c r="B168" s="10"/>
       <c r="C168" s="11"/>
@@ -2950,7 +2974,7 @@
       <c r="H168" s="6"/>
       <c r="I168" s="9"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="10"/>
       <c r="B169" s="10"/>
       <c r="C169" s="11"/>
@@ -2961,7 +2985,7 @@
       <c r="H169" s="6"/>
       <c r="I169" s="9"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="10"/>
       <c r="B170" s="10"/>
       <c r="C170" s="11"/>
@@ -2972,7 +2996,7 @@
       <c r="H170" s="6"/>
       <c r="I170" s="9"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="10"/>
       <c r="B171" s="10"/>
       <c r="C171" s="11"/>
@@ -2983,7 +3007,7 @@
       <c r="H171" s="6"/>
       <c r="I171" s="9"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="10"/>
       <c r="B172" s="10"/>
       <c r="C172" s="11"/>
@@ -2994,7 +3018,7 @@
       <c r="H172" s="6"/>
       <c r="I172" s="9"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="10"/>
       <c r="B173" s="10"/>
       <c r="C173" s="11"/>
@@ -3005,7 +3029,7 @@
       <c r="H173" s="6"/>
       <c r="I173" s="9"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="10"/>
       <c r="B174" s="10"/>
       <c r="C174" s="11"/>
@@ -3016,7 +3040,7 @@
       <c r="H174" s="6"/>
       <c r="I174" s="9"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="10"/>
       <c r="B175" s="10"/>
       <c r="C175" s="11"/>
@@ -3027,7 +3051,7 @@
       <c r="H175" s="6"/>
       <c r="I175" s="9"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="10"/>
       <c r="B176" s="10"/>
       <c r="C176" s="11"/>
@@ -3038,7 +3062,7 @@
       <c r="H176" s="6"/>
       <c r="I176" s="9"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="10"/>
       <c r="B177" s="10"/>
       <c r="C177" s="11"/>
@@ -3049,7 +3073,7 @@
       <c r="H177" s="6"/>
       <c r="I177" s="9"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="10"/>
       <c r="B178" s="10"/>
       <c r="C178" s="11"/>
@@ -3060,7 +3084,7 @@
       <c r="H178" s="6"/>
       <c r="I178" s="9"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="10"/>
       <c r="B179" s="10"/>
       <c r="C179" s="11"/>
@@ -3071,7 +3095,7 @@
       <c r="H179" s="6"/>
       <c r="I179" s="9"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="10"/>
       <c r="B180" s="10"/>
       <c r="C180" s="11"/>
@@ -3082,7 +3106,7 @@
       <c r="H180" s="6"/>
       <c r="I180" s="9"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="10"/>
       <c r="B181" s="10"/>
       <c r="C181" s="11"/>
@@ -3093,7 +3117,7 @@
       <c r="H181" s="6"/>
       <c r="I181" s="9"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182" s="10"/>
       <c r="B182" s="10"/>
       <c r="C182" s="11"/>
@@ -3104,7 +3128,7 @@
       <c r="H182" s="6"/>
       <c r="I182" s="9"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="10"/>
       <c r="B183" s="10"/>
       <c r="C183" s="11"/>
@@ -3115,7 +3139,7 @@
       <c r="H183" s="6"/>
       <c r="I183" s="9"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184" s="10"/>
       <c r="B184" s="10"/>
       <c r="C184" s="11"/>
@@ -3126,7 +3150,7 @@
       <c r="H184" s="6"/>
       <c r="I184" s="9"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A185" s="10"/>
       <c r="B185" s="10"/>
       <c r="C185" s="11"/>
@@ -3137,7 +3161,7 @@
       <c r="H185" s="6"/>
       <c r="I185" s="9"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="10"/>
       <c r="B186" s="10"/>
       <c r="C186" s="11"/>
@@ -3148,7 +3172,7 @@
       <c r="H186" s="6"/>
       <c r="I186" s="9"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187" s="10"/>
       <c r="B187" s="10"/>
       <c r="C187" s="11"/>
@@ -3159,7 +3183,7 @@
       <c r="H187" s="6"/>
       <c r="I187" s="9"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A188" s="10"/>
       <c r="B188" s="10"/>
       <c r="C188" s="11"/>
@@ -3170,7 +3194,7 @@
       <c r="H188" s="6"/>
       <c r="I188" s="9"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A189" s="10"/>
       <c r="B189" s="10"/>
       <c r="C189" s="11"/>
@@ -3181,7 +3205,7 @@
       <c r="H189" s="6"/>
       <c r="I189" s="9"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A190" s="10"/>
       <c r="B190" s="10"/>
       <c r="C190" s="11"/>
@@ -3192,7 +3216,7 @@
       <c r="H190" s="6"/>
       <c r="I190" s="9"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A191" s="10"/>
       <c r="B191" s="10"/>
       <c r="C191" s="11"/>
@@ -3203,7 +3227,7 @@
       <c r="H191" s="6"/>
       <c r="I191" s="9"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A192" s="10"/>
       <c r="B192" s="10"/>
       <c r="C192" s="11"/>
@@ -3214,7 +3238,7 @@
       <c r="H192" s="6"/>
       <c r="I192" s="9"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="10"/>
       <c r="B193" s="10"/>
       <c r="C193" s="11"/>
@@ -3225,7 +3249,7 @@
       <c r="H193" s="6"/>
       <c r="I193" s="9"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="10"/>
       <c r="B194" s="10"/>
       <c r="C194" s="11"/>
@@ -3236,7 +3260,7 @@
       <c r="H194" s="6"/>
       <c r="I194" s="9"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A195" s="10"/>
       <c r="B195" s="10"/>
       <c r="C195" s="11"/>
@@ -3247,7 +3271,7 @@
       <c r="H195" s="6"/>
       <c r="I195" s="9"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A196" s="10"/>
       <c r="B196" s="10"/>
       <c r="C196" s="11"/>
@@ -3258,7 +3282,7 @@
       <c r="H196" s="6"/>
       <c r="I196" s="9"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197" s="10"/>
       <c r="B197" s="10"/>
       <c r="C197" s="11"/>
@@ -3269,7 +3293,7 @@
       <c r="H197" s="6"/>
       <c r="I197" s="9"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A198" s="10"/>
       <c r="B198" s="10"/>
       <c r="C198" s="11"/>
@@ -3280,7 +3304,7 @@
       <c r="H198" s="6"/>
       <c r="I198" s="9"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A199" s="10"/>
       <c r="B199" s="10"/>
       <c r="C199" s="11"/>
@@ -3291,7 +3315,7 @@
       <c r="H199" s="6"/>
       <c r="I199" s="9"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="10"/>
       <c r="B200" s="10"/>
       <c r="C200" s="11"/>
@@ -3302,7 +3326,7 @@
       <c r="H200" s="6"/>
       <c r="I200" s="9"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A201" s="10"/>
       <c r="B201" s="10"/>
       <c r="C201" s="11"/>
@@ -3313,7 +3337,7 @@
       <c r="H201" s="6"/>
       <c r="I201" s="9"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A202" s="10"/>
       <c r="B202" s="10"/>
       <c r="C202" s="11"/>
@@ -3324,7 +3348,7 @@
       <c r="H202" s="6"/>
       <c r="I202" s="9"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203" s="10"/>
       <c r="B203" s="10"/>
       <c r="C203" s="11"/>
@@ -3335,7 +3359,7 @@
       <c r="H203" s="6"/>
       <c r="I203" s="9"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204" s="10"/>
       <c r="B204" s="10"/>
       <c r="C204" s="11"/>
@@ -3346,7 +3370,7 @@
       <c r="H204" s="6"/>
       <c r="I204" s="9"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205" s="10"/>
       <c r="B205" s="10"/>
       <c r="C205" s="11"/>
@@ -3357,7 +3381,7 @@
       <c r="H205" s="6"/>
       <c r="I205" s="9"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206" s="10"/>
       <c r="B206" s="10"/>
       <c r="C206" s="11"/>
@@ -3368,7 +3392,7 @@
       <c r="H206" s="6"/>
       <c r="I206" s="9"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="10"/>
       <c r="B207" s="10"/>
       <c r="C207" s="11"/>
@@ -3379,7 +3403,7 @@
       <c r="H207" s="6"/>
       <c r="I207" s="9"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="10"/>
       <c r="B208" s="10"/>
       <c r="C208" s="11"/>
@@ -3390,7 +3414,7 @@
       <c r="H208" s="6"/>
       <c r="I208" s="9"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="10"/>
       <c r="B209" s="10"/>
       <c r="C209" s="11"/>
@@ -3401,7 +3425,7 @@
       <c r="H209" s="6"/>
       <c r="I209" s="9"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="10"/>
       <c r="B210" s="10"/>
       <c r="C210" s="11"/>
@@ -3412,7 +3436,7 @@
       <c r="H210" s="6"/>
       <c r="I210" s="9"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211" s="10"/>
       <c r="B211" s="10"/>
       <c r="C211" s="11"/>
@@ -3423,7 +3447,7 @@
       <c r="H211" s="6"/>
       <c r="I211" s="9"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212" s="10"/>
       <c r="B212" s="10"/>
       <c r="C212" s="11"/>
@@ -3434,7 +3458,7 @@
       <c r="H212" s="6"/>
       <c r="I212" s="9"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213" s="10"/>
       <c r="B213" s="10"/>
       <c r="C213" s="11"/>
@@ -3445,7 +3469,7 @@
       <c r="H213" s="6"/>
       <c r="I213" s="9"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="10"/>
       <c r="B214" s="10"/>
       <c r="C214" s="11"/>
@@ -3456,7 +3480,7 @@
       <c r="H214" s="6"/>
       <c r="I214" s="9"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A215" s="10"/>
       <c r="B215" s="10"/>
       <c r="C215" s="11"/>
@@ -3467,7 +3491,7 @@
       <c r="H215" s="6"/>
       <c r="I215" s="9"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A216" s="10"/>
       <c r="B216" s="10"/>
       <c r="C216" s="11"/>
@@ -3478,7 +3502,7 @@
       <c r="H216" s="6"/>
       <c r="I216" s="9"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A217" s="10"/>
       <c r="B217" s="10"/>
       <c r="C217" s="11"/>
@@ -3489,7 +3513,7 @@
       <c r="H217" s="6"/>
       <c r="I217" s="9"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A218" s="10"/>
       <c r="B218" s="10"/>
       <c r="C218" s="11"/>
@@ -3500,7 +3524,7 @@
       <c r="H218" s="6"/>
       <c r="I218" s="9"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A219" s="10"/>
       <c r="B219" s="10"/>
       <c r="C219" s="11"/>
@@ -3511,2359 +3535,2358 @@
       <c r="H219" s="6"/>
       <c r="I219" s="9"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H220" s="3"/>
       <c r="I220" s="9"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
+    <row r="221" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H221" s="3"/>
       <c r="I221" s="9"/>
     </row>
-    <row r="222" ht="15.75" customHeight="1">
+    <row r="222" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H222" s="3"/>
       <c r="I222" s="9"/>
     </row>
-    <row r="223" ht="15.75" customHeight="1">
+    <row r="223" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H223" s="3"/>
       <c r="I223" s="9"/>
     </row>
-    <row r="224" ht="15.75" customHeight="1">
+    <row r="224" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H224" s="3"/>
       <c r="I224" s="9"/>
     </row>
-    <row r="225" ht="15.75" customHeight="1">
+    <row r="225" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H225" s="3"/>
       <c r="I225" s="9"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1">
+    <row r="226" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H226" s="3"/>
     </row>
-    <row r="227" ht="15.75" customHeight="1">
+    <row r="227" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H227" s="3"/>
     </row>
-    <row r="228" ht="15.75" customHeight="1">
+    <row r="228" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H228" s="3"/>
     </row>
-    <row r="229" ht="15.75" customHeight="1">
+    <row r="229" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H229" s="3"/>
     </row>
-    <row r="230" ht="15.75" customHeight="1">
+    <row r="230" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H230" s="3"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1">
+    <row r="231" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H231" s="3"/>
     </row>
-    <row r="232" ht="15.75" customHeight="1">
+    <row r="232" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H232" s="3"/>
     </row>
-    <row r="233" ht="15.75" customHeight="1">
+    <row r="233" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H233" s="3"/>
     </row>
-    <row r="234" ht="15.75" customHeight="1">
+    <row r="234" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H234" s="3"/>
     </row>
-    <row r="235" ht="15.75" customHeight="1">
+    <row r="235" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H235" s="3"/>
     </row>
-    <row r="236" ht="15.75" customHeight="1">
+    <row r="236" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H236" s="3"/>
     </row>
-    <row r="237" ht="15.75" customHeight="1">
+    <row r="237" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H237" s="3"/>
     </row>
-    <row r="238" ht="15.75" customHeight="1">
+    <row r="238" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H238" s="3"/>
     </row>
-    <row r="239" ht="15.75" customHeight="1">
+    <row r="239" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H239" s="3"/>
     </row>
-    <row r="240" ht="15.75" customHeight="1">
+    <row r="240" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H240" s="3"/>
     </row>
-    <row r="241" ht="15.75" customHeight="1">
+    <row r="241" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H241" s="3"/>
     </row>
-    <row r="242" ht="15.75" customHeight="1">
+    <row r="242" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H242" s="3"/>
     </row>
-    <row r="243" ht="15.75" customHeight="1">
+    <row r="243" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H243" s="3"/>
     </row>
-    <row r="244" ht="15.75" customHeight="1">
+    <row r="244" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H244" s="3"/>
     </row>
-    <row r="245" ht="15.75" customHeight="1">
+    <row r="245" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H245" s="3"/>
     </row>
-    <row r="246" ht="15.75" customHeight="1">
+    <row r="246" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H246" s="3"/>
     </row>
-    <row r="247" ht="15.75" customHeight="1">
+    <row r="247" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H247" s="3"/>
     </row>
-    <row r="248" ht="15.75" customHeight="1">
+    <row r="248" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H248" s="3"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1">
+    <row r="249" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H249" s="3"/>
     </row>
-    <row r="250" ht="15.75" customHeight="1">
+    <row r="250" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H250" s="3"/>
     </row>
-    <row r="251" ht="15.75" customHeight="1">
+    <row r="251" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H251" s="3"/>
     </row>
-    <row r="252" ht="15.75" customHeight="1">
+    <row r="252" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H252" s="3"/>
     </row>
-    <row r="253" ht="15.75" customHeight="1">
+    <row r="253" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H253" s="3"/>
     </row>
-    <row r="254" ht="15.75" customHeight="1">
+    <row r="254" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H254" s="3"/>
     </row>
-    <row r="255" ht="15.75" customHeight="1">
+    <row r="255" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H255" s="3"/>
     </row>
-    <row r="256" ht="15.75" customHeight="1">
+    <row r="256" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H256" s="3"/>
     </row>
-    <row r="257" ht="15.75" customHeight="1">
+    <row r="257" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H257" s="3"/>
     </row>
-    <row r="258" ht="15.75" customHeight="1">
+    <row r="258" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H258" s="3"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1">
+    <row r="259" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H259" s="3"/>
     </row>
-    <row r="260" ht="15.75" customHeight="1">
+    <row r="260" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H260" s="3"/>
     </row>
-    <row r="261" ht="15.75" customHeight="1">
+    <row r="261" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H261" s="3"/>
     </row>
-    <row r="262" ht="15.75" customHeight="1">
+    <row r="262" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H262" s="3"/>
     </row>
-    <row r="263" ht="15.75" customHeight="1">
+    <row r="263" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H263" s="3"/>
     </row>
-    <row r="264" ht="15.75" customHeight="1">
+    <row r="264" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H264" s="3"/>
     </row>
-    <row r="265" ht="15.75" customHeight="1">
+    <row r="265" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H265" s="3"/>
     </row>
-    <row r="266" ht="15.75" customHeight="1">
+    <row r="266" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H266" s="3"/>
     </row>
-    <row r="267" ht="15.75" customHeight="1">
+    <row r="267" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H267" s="3"/>
     </row>
-    <row r="268" ht="15.75" customHeight="1">
+    <row r="268" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H268" s="3"/>
     </row>
-    <row r="269" ht="15.75" customHeight="1">
+    <row r="269" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H269" s="3"/>
     </row>
-    <row r="270" ht="15.75" customHeight="1">
+    <row r="270" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H270" s="3"/>
     </row>
-    <row r="271" ht="15.75" customHeight="1">
+    <row r="271" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H271" s="3"/>
     </row>
-    <row r="272" ht="15.75" customHeight="1">
+    <row r="272" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H272" s="3"/>
     </row>
-    <row r="273" ht="15.75" customHeight="1">
+    <row r="273" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H273" s="3"/>
     </row>
-    <row r="274" ht="15.75" customHeight="1">
+    <row r="274" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H274" s="3"/>
     </row>
-    <row r="275" ht="15.75" customHeight="1">
+    <row r="275" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H275" s="3"/>
     </row>
-    <row r="276" ht="15.75" customHeight="1">
+    <row r="276" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H276" s="3"/>
     </row>
-    <row r="277" ht="15.75" customHeight="1">
+    <row r="277" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H277" s="3"/>
     </row>
-    <row r="278" ht="15.75" customHeight="1">
+    <row r="278" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H278" s="3"/>
     </row>
-    <row r="279" ht="15.75" customHeight="1">
+    <row r="279" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H279" s="3"/>
     </row>
-    <row r="280" ht="15.75" customHeight="1">
+    <row r="280" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H280" s="3"/>
     </row>
-    <row r="281" ht="15.75" customHeight="1">
+    <row r="281" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H281" s="3"/>
     </row>
-    <row r="282" ht="15.75" customHeight="1">
+    <row r="282" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H282" s="3"/>
     </row>
-    <row r="283" ht="15.75" customHeight="1">
+    <row r="283" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H283" s="3"/>
     </row>
-    <row r="284" ht="15.75" customHeight="1">
+    <row r="284" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H284" s="3"/>
     </row>
-    <row r="285" ht="15.75" customHeight="1">
+    <row r="285" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H285" s="3"/>
     </row>
-    <row r="286" ht="15.75" customHeight="1">
+    <row r="286" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H286" s="3"/>
     </row>
-    <row r="287" ht="15.75" customHeight="1">
+    <row r="287" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H287" s="3"/>
     </row>
-    <row r="288" ht="15.75" customHeight="1">
+    <row r="288" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H288" s="3"/>
     </row>
-    <row r="289" ht="15.75" customHeight="1">
+    <row r="289" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H289" s="3"/>
     </row>
-    <row r="290" ht="15.75" customHeight="1">
+    <row r="290" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H290" s="3"/>
     </row>
-    <row r="291" ht="15.75" customHeight="1">
+    <row r="291" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H291" s="3"/>
     </row>
-    <row r="292" ht="15.75" customHeight="1">
+    <row r="292" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H292" s="3"/>
     </row>
-    <row r="293" ht="15.75" customHeight="1">
+    <row r="293" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H293" s="3"/>
     </row>
-    <row r="294" ht="15.75" customHeight="1">
+    <row r="294" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H294" s="3"/>
     </row>
-    <row r="295" ht="15.75" customHeight="1">
+    <row r="295" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H295" s="3"/>
     </row>
-    <row r="296" ht="15.75" customHeight="1">
+    <row r="296" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H296" s="3"/>
     </row>
-    <row r="297" ht="15.75" customHeight="1">
+    <row r="297" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H297" s="3"/>
     </row>
-    <row r="298" ht="15.75" customHeight="1">
+    <row r="298" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H298" s="3"/>
     </row>
-    <row r="299" ht="15.75" customHeight="1">
+    <row r="299" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H299" s="3"/>
     </row>
-    <row r="300" ht="15.75" customHeight="1">
+    <row r="300" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H300" s="3"/>
     </row>
-    <row r="301" ht="15.75" customHeight="1">
+    <row r="301" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H301" s="3"/>
     </row>
-    <row r="302" ht="15.75" customHeight="1">
+    <row r="302" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H302" s="3"/>
     </row>
-    <row r="303" ht="15.75" customHeight="1">
+    <row r="303" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H303" s="3"/>
     </row>
-    <row r="304" ht="15.75" customHeight="1">
+    <row r="304" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H304" s="3"/>
     </row>
-    <row r="305" ht="15.75" customHeight="1">
+    <row r="305" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H305" s="3"/>
     </row>
-    <row r="306" ht="15.75" customHeight="1">
+    <row r="306" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H306" s="3"/>
     </row>
-    <row r="307" ht="15.75" customHeight="1">
+    <row r="307" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H307" s="3"/>
     </row>
-    <row r="308" ht="15.75" customHeight="1">
+    <row r="308" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H308" s="3"/>
     </row>
-    <row r="309" ht="15.75" customHeight="1">
+    <row r="309" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H309" s="3"/>
     </row>
-    <row r="310" ht="15.75" customHeight="1">
+    <row r="310" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H310" s="3"/>
     </row>
-    <row r="311" ht="15.75" customHeight="1">
+    <row r="311" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H311" s="3"/>
     </row>
-    <row r="312" ht="15.75" customHeight="1">
+    <row r="312" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H312" s="3"/>
     </row>
-    <row r="313" ht="15.75" customHeight="1">
+    <row r="313" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H313" s="3"/>
     </row>
-    <row r="314" ht="15.75" customHeight="1">
+    <row r="314" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H314" s="3"/>
     </row>
-    <row r="315" ht="15.75" customHeight="1">
+    <row r="315" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H315" s="3"/>
     </row>
-    <row r="316" ht="15.75" customHeight="1">
+    <row r="316" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H316" s="3"/>
     </row>
-    <row r="317" ht="15.75" customHeight="1">
+    <row r="317" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H317" s="3"/>
     </row>
-    <row r="318" ht="15.75" customHeight="1">
+    <row r="318" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H318" s="3"/>
     </row>
-    <row r="319" ht="15.75" customHeight="1">
+    <row r="319" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H319" s="3"/>
     </row>
-    <row r="320" ht="15.75" customHeight="1">
+    <row r="320" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H320" s="3"/>
     </row>
-    <row r="321" ht="15.75" customHeight="1">
+    <row r="321" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H321" s="3"/>
     </row>
-    <row r="322" ht="15.75" customHeight="1">
+    <row r="322" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H322" s="3"/>
     </row>
-    <row r="323" ht="15.75" customHeight="1">
+    <row r="323" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H323" s="3"/>
     </row>
-    <row r="324" ht="15.75" customHeight="1">
+    <row r="324" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H324" s="3"/>
     </row>
-    <row r="325" ht="15.75" customHeight="1">
+    <row r="325" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H325" s="3"/>
     </row>
-    <row r="326" ht="15.75" customHeight="1">
+    <row r="326" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H326" s="3"/>
     </row>
-    <row r="327" ht="15.75" customHeight="1">
+    <row r="327" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H327" s="3"/>
     </row>
-    <row r="328" ht="15.75" customHeight="1">
+    <row r="328" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H328" s="3"/>
     </row>
-    <row r="329" ht="15.75" customHeight="1">
+    <row r="329" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H329" s="3"/>
     </row>
-    <row r="330" ht="15.75" customHeight="1">
+    <row r="330" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H330" s="3"/>
     </row>
-    <row r="331" ht="15.75" customHeight="1">
+    <row r="331" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H331" s="3"/>
     </row>
-    <row r="332" ht="15.75" customHeight="1">
+    <row r="332" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H332" s="3"/>
     </row>
-    <row r="333" ht="15.75" customHeight="1">
+    <row r="333" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H333" s="3"/>
     </row>
-    <row r="334" ht="15.75" customHeight="1">
+    <row r="334" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H334" s="3"/>
     </row>
-    <row r="335" ht="15.75" customHeight="1">
+    <row r="335" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H335" s="3"/>
     </row>
-    <row r="336" ht="15.75" customHeight="1">
+    <row r="336" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H336" s="3"/>
     </row>
-    <row r="337" ht="15.75" customHeight="1">
+    <row r="337" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H337" s="3"/>
     </row>
-    <row r="338" ht="15.75" customHeight="1">
+    <row r="338" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H338" s="3"/>
     </row>
-    <row r="339" ht="15.75" customHeight="1">
+    <row r="339" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H339" s="3"/>
     </row>
-    <row r="340" ht="15.75" customHeight="1">
+    <row r="340" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H340" s="3"/>
     </row>
-    <row r="341" ht="15.75" customHeight="1">
+    <row r="341" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H341" s="3"/>
     </row>
-    <row r="342" ht="15.75" customHeight="1">
+    <row r="342" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H342" s="3"/>
     </row>
-    <row r="343" ht="15.75" customHeight="1">
+    <row r="343" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H343" s="3"/>
     </row>
-    <row r="344" ht="15.75" customHeight="1">
+    <row r="344" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H344" s="3"/>
     </row>
-    <row r="345" ht="15.75" customHeight="1">
+    <row r="345" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H345" s="3"/>
     </row>
-    <row r="346" ht="15.75" customHeight="1">
+    <row r="346" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H346" s="3"/>
     </row>
-    <row r="347" ht="15.75" customHeight="1">
+    <row r="347" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H347" s="3"/>
     </row>
-    <row r="348" ht="15.75" customHeight="1">
+    <row r="348" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H348" s="3"/>
     </row>
-    <row r="349" ht="15.75" customHeight="1">
+    <row r="349" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H349" s="3"/>
     </row>
-    <row r="350" ht="15.75" customHeight="1">
+    <row r="350" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H350" s="3"/>
     </row>
-    <row r="351" ht="15.75" customHeight="1">
+    <row r="351" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H351" s="3"/>
     </row>
-    <row r="352" ht="15.75" customHeight="1">
+    <row r="352" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H352" s="3"/>
     </row>
-    <row r="353" ht="15.75" customHeight="1">
+    <row r="353" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H353" s="3"/>
     </row>
-    <row r="354" ht="15.75" customHeight="1">
+    <row r="354" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H354" s="3"/>
     </row>
-    <row r="355" ht="15.75" customHeight="1">
+    <row r="355" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H355" s="3"/>
     </row>
-    <row r="356" ht="15.75" customHeight="1">
+    <row r="356" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H356" s="3"/>
     </row>
-    <row r="357" ht="15.75" customHeight="1">
+    <row r="357" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H357" s="3"/>
     </row>
-    <row r="358" ht="15.75" customHeight="1">
+    <row r="358" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H358" s="3"/>
     </row>
-    <row r="359" ht="15.75" customHeight="1">
+    <row r="359" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H359" s="3"/>
     </row>
-    <row r="360" ht="15.75" customHeight="1">
+    <row r="360" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H360" s="3"/>
     </row>
-    <row r="361" ht="15.75" customHeight="1">
+    <row r="361" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H361" s="3"/>
     </row>
-    <row r="362" ht="15.75" customHeight="1">
+    <row r="362" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H362" s="3"/>
     </row>
-    <row r="363" ht="15.75" customHeight="1">
+    <row r="363" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H363" s="3"/>
     </row>
-    <row r="364" ht="15.75" customHeight="1">
+    <row r="364" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H364" s="3"/>
     </row>
-    <row r="365" ht="15.75" customHeight="1">
+    <row r="365" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H365" s="3"/>
     </row>
-    <row r="366" ht="15.75" customHeight="1">
+    <row r="366" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H366" s="3"/>
     </row>
-    <row r="367" ht="15.75" customHeight="1">
+    <row r="367" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H367" s="3"/>
     </row>
-    <row r="368" ht="15.75" customHeight="1">
+    <row r="368" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H368" s="3"/>
     </row>
-    <row r="369" ht="15.75" customHeight="1">
+    <row r="369" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H369" s="3"/>
     </row>
-    <row r="370" ht="15.75" customHeight="1">
+    <row r="370" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H370" s="3"/>
     </row>
-    <row r="371" ht="15.75" customHeight="1">
+    <row r="371" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H371" s="3"/>
     </row>
-    <row r="372" ht="15.75" customHeight="1">
+    <row r="372" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H372" s="3"/>
     </row>
-    <row r="373" ht="15.75" customHeight="1">
+    <row r="373" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H373" s="3"/>
     </row>
-    <row r="374" ht="15.75" customHeight="1">
+    <row r="374" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H374" s="3"/>
     </row>
-    <row r="375" ht="15.75" customHeight="1">
+    <row r="375" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H375" s="3"/>
     </row>
-    <row r="376" ht="15.75" customHeight="1">
+    <row r="376" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H376" s="3"/>
     </row>
-    <row r="377" ht="15.75" customHeight="1">
+    <row r="377" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H377" s="3"/>
     </row>
-    <row r="378" ht="15.75" customHeight="1">
+    <row r="378" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H378" s="3"/>
     </row>
-    <row r="379" ht="15.75" customHeight="1">
+    <row r="379" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H379" s="3"/>
     </row>
-    <row r="380" ht="15.75" customHeight="1">
+    <row r="380" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H380" s="3"/>
     </row>
-    <row r="381" ht="15.75" customHeight="1">
+    <row r="381" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H381" s="3"/>
     </row>
-    <row r="382" ht="15.75" customHeight="1">
+    <row r="382" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H382" s="3"/>
     </row>
-    <row r="383" ht="15.75" customHeight="1">
+    <row r="383" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H383" s="3"/>
     </row>
-    <row r="384" ht="15.75" customHeight="1">
+    <row r="384" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H384" s="3"/>
     </row>
-    <row r="385" ht="15.75" customHeight="1">
+    <row r="385" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H385" s="3"/>
     </row>
-    <row r="386" ht="15.75" customHeight="1">
+    <row r="386" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H386" s="3"/>
     </row>
-    <row r="387" ht="15.75" customHeight="1">
+    <row r="387" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H387" s="3"/>
     </row>
-    <row r="388" ht="15.75" customHeight="1">
+    <row r="388" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H388" s="3"/>
     </row>
-    <row r="389" ht="15.75" customHeight="1">
+    <row r="389" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H389" s="3"/>
     </row>
-    <row r="390" ht="15.75" customHeight="1">
+    <row r="390" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H390" s="3"/>
     </row>
-    <row r="391" ht="15.75" customHeight="1">
+    <row r="391" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H391" s="3"/>
     </row>
-    <row r="392" ht="15.75" customHeight="1">
+    <row r="392" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H392" s="3"/>
     </row>
-    <row r="393" ht="15.75" customHeight="1">
+    <row r="393" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H393" s="3"/>
     </row>
-    <row r="394" ht="15.75" customHeight="1">
+    <row r="394" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H394" s="3"/>
     </row>
-    <row r="395" ht="15.75" customHeight="1">
+    <row r="395" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H395" s="3"/>
     </row>
-    <row r="396" ht="15.75" customHeight="1">
+    <row r="396" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H396" s="3"/>
     </row>
-    <row r="397" ht="15.75" customHeight="1">
+    <row r="397" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H397" s="3"/>
     </row>
-    <row r="398" ht="15.75" customHeight="1">
+    <row r="398" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H398" s="3"/>
     </row>
-    <row r="399" ht="15.75" customHeight="1">
+    <row r="399" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H399" s="3"/>
     </row>
-    <row r="400" ht="15.75" customHeight="1">
+    <row r="400" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H400" s="3"/>
     </row>
-    <row r="401" ht="15.75" customHeight="1">
+    <row r="401" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H401" s="3"/>
     </row>
-    <row r="402" ht="15.75" customHeight="1">
+    <row r="402" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H402" s="3"/>
     </row>
-    <row r="403" ht="15.75" customHeight="1">
+    <row r="403" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H403" s="3"/>
     </row>
-    <row r="404" ht="15.75" customHeight="1">
+    <row r="404" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H404" s="3"/>
     </row>
-    <row r="405" ht="15.75" customHeight="1">
+    <row r="405" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H405" s="3"/>
     </row>
-    <row r="406" ht="15.75" customHeight="1">
+    <row r="406" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H406" s="3"/>
     </row>
-    <row r="407" ht="15.75" customHeight="1">
+    <row r="407" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H407" s="3"/>
     </row>
-    <row r="408" ht="15.75" customHeight="1">
+    <row r="408" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H408" s="3"/>
     </row>
-    <row r="409" ht="15.75" customHeight="1">
+    <row r="409" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H409" s="3"/>
     </row>
-    <row r="410" ht="15.75" customHeight="1">
+    <row r="410" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H410" s="3"/>
     </row>
-    <row r="411" ht="15.75" customHeight="1">
+    <row r="411" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H411" s="3"/>
     </row>
-    <row r="412" ht="15.75" customHeight="1">
+    <row r="412" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H412" s="3"/>
     </row>
-    <row r="413" ht="15.75" customHeight="1">
+    <row r="413" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H413" s="3"/>
     </row>
-    <row r="414" ht="15.75" customHeight="1">
+    <row r="414" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H414" s="3"/>
     </row>
-    <row r="415" ht="15.75" customHeight="1">
+    <row r="415" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H415" s="3"/>
     </row>
-    <row r="416" ht="15.75" customHeight="1">
+    <row r="416" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H416" s="3"/>
     </row>
-    <row r="417" ht="15.75" customHeight="1">
+    <row r="417" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H417" s="3"/>
     </row>
-    <row r="418" ht="15.75" customHeight="1">
+    <row r="418" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H418" s="3"/>
     </row>
-    <row r="419" ht="15.75" customHeight="1">
+    <row r="419" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H419" s="3"/>
     </row>
-    <row r="420" ht="15.75" customHeight="1">
+    <row r="420" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H420" s="3"/>
     </row>
-    <row r="421" ht="15.75" customHeight="1">
+    <row r="421" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H421" s="3"/>
     </row>
-    <row r="422" ht="15.75" customHeight="1">
+    <row r="422" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H422" s="3"/>
     </row>
-    <row r="423" ht="15.75" customHeight="1">
+    <row r="423" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H423" s="3"/>
     </row>
-    <row r="424" ht="15.75" customHeight="1">
+    <row r="424" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H424" s="3"/>
     </row>
-    <row r="425" ht="15.75" customHeight="1">
+    <row r="425" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H425" s="3"/>
     </row>
-    <row r="426" ht="15.75" customHeight="1">
+    <row r="426" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H426" s="3"/>
     </row>
-    <row r="427" ht="15.75" customHeight="1">
+    <row r="427" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H427" s="3"/>
     </row>
-    <row r="428" ht="15.75" customHeight="1">
+    <row r="428" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H428" s="3"/>
     </row>
-    <row r="429" ht="15.75" customHeight="1">
+    <row r="429" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H429" s="3"/>
     </row>
-    <row r="430" ht="15.75" customHeight="1">
+    <row r="430" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H430" s="3"/>
     </row>
-    <row r="431" ht="15.75" customHeight="1">
+    <row r="431" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H431" s="3"/>
     </row>
-    <row r="432" ht="15.75" customHeight="1">
+    <row r="432" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H432" s="3"/>
     </row>
-    <row r="433" ht="15.75" customHeight="1">
+    <row r="433" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H433" s="3"/>
     </row>
-    <row r="434" ht="15.75" customHeight="1">
+    <row r="434" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H434" s="3"/>
     </row>
-    <row r="435" ht="15.75" customHeight="1">
+    <row r="435" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H435" s="3"/>
     </row>
-    <row r="436" ht="15.75" customHeight="1">
+    <row r="436" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H436" s="3"/>
     </row>
-    <row r="437" ht="15.75" customHeight="1">
+    <row r="437" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H437" s="3"/>
     </row>
-    <row r="438" ht="15.75" customHeight="1">
+    <row r="438" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H438" s="3"/>
     </row>
-    <row r="439" ht="15.75" customHeight="1">
+    <row r="439" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H439" s="3"/>
     </row>
-    <row r="440" ht="15.75" customHeight="1">
+    <row r="440" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H440" s="3"/>
     </row>
-    <row r="441" ht="15.75" customHeight="1">
+    <row r="441" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H441" s="3"/>
     </row>
-    <row r="442" ht="15.75" customHeight="1">
+    <row r="442" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H442" s="3"/>
     </row>
-    <row r="443" ht="15.75" customHeight="1">
+    <row r="443" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H443" s="3"/>
     </row>
-    <row r="444" ht="15.75" customHeight="1">
+    <row r="444" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H444" s="3"/>
     </row>
-    <row r="445" ht="15.75" customHeight="1">
+    <row r="445" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H445" s="3"/>
     </row>
-    <row r="446" ht="15.75" customHeight="1">
+    <row r="446" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H446" s="3"/>
     </row>
-    <row r="447" ht="15.75" customHeight="1">
+    <row r="447" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H447" s="3"/>
     </row>
-    <row r="448" ht="15.75" customHeight="1">
+    <row r="448" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H448" s="3"/>
     </row>
-    <row r="449" ht="15.75" customHeight="1">
+    <row r="449" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H449" s="3"/>
     </row>
-    <row r="450" ht="15.75" customHeight="1">
+    <row r="450" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H450" s="3"/>
     </row>
-    <row r="451" ht="15.75" customHeight="1">
+    <row r="451" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H451" s="3"/>
     </row>
-    <row r="452" ht="15.75" customHeight="1">
+    <row r="452" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H452" s="3"/>
     </row>
-    <row r="453" ht="15.75" customHeight="1">
+    <row r="453" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H453" s="3"/>
     </row>
-    <row r="454" ht="15.75" customHeight="1">
+    <row r="454" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H454" s="3"/>
     </row>
-    <row r="455" ht="15.75" customHeight="1">
+    <row r="455" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H455" s="3"/>
     </row>
-    <row r="456" ht="15.75" customHeight="1">
+    <row r="456" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H456" s="3"/>
     </row>
-    <row r="457" ht="15.75" customHeight="1">
+    <row r="457" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H457" s="3"/>
     </row>
-    <row r="458" ht="15.75" customHeight="1">
+    <row r="458" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H458" s="3"/>
     </row>
-    <row r="459" ht="15.75" customHeight="1">
+    <row r="459" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H459" s="3"/>
     </row>
-    <row r="460" ht="15.75" customHeight="1">
+    <row r="460" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H460" s="3"/>
     </row>
-    <row r="461" ht="15.75" customHeight="1">
+    <row r="461" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H461" s="3"/>
     </row>
-    <row r="462" ht="15.75" customHeight="1">
+    <row r="462" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H462" s="3"/>
     </row>
-    <row r="463" ht="15.75" customHeight="1">
+    <row r="463" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H463" s="3"/>
     </row>
-    <row r="464" ht="15.75" customHeight="1">
+    <row r="464" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H464" s="3"/>
     </row>
-    <row r="465" ht="15.75" customHeight="1">
+    <row r="465" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H465" s="3"/>
     </row>
-    <row r="466" ht="15.75" customHeight="1">
+    <row r="466" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H466" s="3"/>
     </row>
-    <row r="467" ht="15.75" customHeight="1">
+    <row r="467" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H467" s="3"/>
     </row>
-    <row r="468" ht="15.75" customHeight="1">
+    <row r="468" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H468" s="3"/>
     </row>
-    <row r="469" ht="15.75" customHeight="1">
+    <row r="469" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H469" s="3"/>
     </row>
-    <row r="470" ht="15.75" customHeight="1">
+    <row r="470" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H470" s="3"/>
     </row>
-    <row r="471" ht="15.75" customHeight="1">
+    <row r="471" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H471" s="3"/>
     </row>
-    <row r="472" ht="15.75" customHeight="1">
+    <row r="472" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H472" s="3"/>
     </row>
-    <row r="473" ht="15.75" customHeight="1">
+    <row r="473" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H473" s="3"/>
     </row>
-    <row r="474" ht="15.75" customHeight="1">
+    <row r="474" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H474" s="3"/>
     </row>
-    <row r="475" ht="15.75" customHeight="1">
+    <row r="475" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H475" s="3"/>
     </row>
-    <row r="476" ht="15.75" customHeight="1">
+    <row r="476" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H476" s="3"/>
     </row>
-    <row r="477" ht="15.75" customHeight="1">
+    <row r="477" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H477" s="3"/>
     </row>
-    <row r="478" ht="15.75" customHeight="1">
+    <row r="478" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H478" s="3"/>
     </row>
-    <row r="479" ht="15.75" customHeight="1">
+    <row r="479" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H479" s="3"/>
     </row>
-    <row r="480" ht="15.75" customHeight="1">
+    <row r="480" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H480" s="3"/>
     </row>
-    <row r="481" ht="15.75" customHeight="1">
+    <row r="481" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H481" s="3"/>
     </row>
-    <row r="482" ht="15.75" customHeight="1">
+    <row r="482" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H482" s="3"/>
     </row>
-    <row r="483" ht="15.75" customHeight="1">
+    <row r="483" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H483" s="3"/>
     </row>
-    <row r="484" ht="15.75" customHeight="1">
+    <row r="484" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H484" s="3"/>
     </row>
-    <row r="485" ht="15.75" customHeight="1">
+    <row r="485" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H485" s="3"/>
     </row>
-    <row r="486" ht="15.75" customHeight="1">
+    <row r="486" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H486" s="3"/>
     </row>
-    <row r="487" ht="15.75" customHeight="1">
+    <row r="487" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H487" s="3"/>
     </row>
-    <row r="488" ht="15.75" customHeight="1">
+    <row r="488" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H488" s="3"/>
     </row>
-    <row r="489" ht="15.75" customHeight="1">
+    <row r="489" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H489" s="3"/>
     </row>
-    <row r="490" ht="15.75" customHeight="1">
+    <row r="490" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H490" s="3"/>
     </row>
-    <row r="491" ht="15.75" customHeight="1">
+    <row r="491" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H491" s="3"/>
     </row>
-    <row r="492" ht="15.75" customHeight="1">
+    <row r="492" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H492" s="3"/>
     </row>
-    <row r="493" ht="15.75" customHeight="1">
+    <row r="493" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H493" s="3"/>
     </row>
-    <row r="494" ht="15.75" customHeight="1">
+    <row r="494" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H494" s="3"/>
     </row>
-    <row r="495" ht="15.75" customHeight="1">
+    <row r="495" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H495" s="3"/>
     </row>
-    <row r="496" ht="15.75" customHeight="1">
+    <row r="496" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H496" s="3"/>
     </row>
-    <row r="497" ht="15.75" customHeight="1">
+    <row r="497" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H497" s="3"/>
     </row>
-    <row r="498" ht="15.75" customHeight="1">
+    <row r="498" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H498" s="3"/>
     </row>
-    <row r="499" ht="15.75" customHeight="1">
+    <row r="499" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H499" s="3"/>
     </row>
-    <row r="500" ht="15.75" customHeight="1">
+    <row r="500" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H500" s="3"/>
     </row>
-    <row r="501" ht="15.75" customHeight="1">
+    <row r="501" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H501" s="3"/>
     </row>
-    <row r="502" ht="15.75" customHeight="1">
+    <row r="502" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H502" s="3"/>
     </row>
-    <row r="503" ht="15.75" customHeight="1">
+    <row r="503" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H503" s="3"/>
     </row>
-    <row r="504" ht="15.75" customHeight="1">
+    <row r="504" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H504" s="3"/>
     </row>
-    <row r="505" ht="15.75" customHeight="1">
+    <row r="505" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H505" s="3"/>
     </row>
-    <row r="506" ht="15.75" customHeight="1">
+    <row r="506" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H506" s="3"/>
     </row>
-    <row r="507" ht="15.75" customHeight="1">
+    <row r="507" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H507" s="3"/>
     </row>
-    <row r="508" ht="15.75" customHeight="1">
+    <row r="508" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H508" s="3"/>
     </row>
-    <row r="509" ht="15.75" customHeight="1">
+    <row r="509" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H509" s="3"/>
     </row>
-    <row r="510" ht="15.75" customHeight="1">
+    <row r="510" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H510" s="3"/>
     </row>
-    <row r="511" ht="15.75" customHeight="1">
+    <row r="511" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H511" s="3"/>
     </row>
-    <row r="512" ht="15.75" customHeight="1">
+    <row r="512" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H512" s="3"/>
     </row>
-    <row r="513" ht="15.75" customHeight="1">
+    <row r="513" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H513" s="3"/>
     </row>
-    <row r="514" ht="15.75" customHeight="1">
+    <row r="514" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H514" s="3"/>
     </row>
-    <row r="515" ht="15.75" customHeight="1">
+    <row r="515" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H515" s="3"/>
     </row>
-    <row r="516" ht="15.75" customHeight="1">
+    <row r="516" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H516" s="3"/>
     </row>
-    <row r="517" ht="15.75" customHeight="1">
+    <row r="517" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H517" s="3"/>
     </row>
-    <row r="518" ht="15.75" customHeight="1">
+    <row r="518" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H518" s="3"/>
     </row>
-    <row r="519" ht="15.75" customHeight="1">
+    <row r="519" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H519" s="3"/>
     </row>
-    <row r="520" ht="15.75" customHeight="1">
+    <row r="520" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H520" s="3"/>
     </row>
-    <row r="521" ht="15.75" customHeight="1">
+    <row r="521" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H521" s="3"/>
     </row>
-    <row r="522" ht="15.75" customHeight="1">
+    <row r="522" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H522" s="3"/>
     </row>
-    <row r="523" ht="15.75" customHeight="1">
+    <row r="523" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H523" s="3"/>
     </row>
-    <row r="524" ht="15.75" customHeight="1">
+    <row r="524" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H524" s="3"/>
     </row>
-    <row r="525" ht="15.75" customHeight="1">
+    <row r="525" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H525" s="3"/>
     </row>
-    <row r="526" ht="15.75" customHeight="1">
+    <row r="526" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H526" s="3"/>
     </row>
-    <row r="527" ht="15.75" customHeight="1">
+    <row r="527" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H527" s="3"/>
     </row>
-    <row r="528" ht="15.75" customHeight="1">
+    <row r="528" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H528" s="3"/>
     </row>
-    <row r="529" ht="15.75" customHeight="1">
+    <row r="529" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H529" s="3"/>
     </row>
-    <row r="530" ht="15.75" customHeight="1">
+    <row r="530" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H530" s="3"/>
     </row>
-    <row r="531" ht="15.75" customHeight="1">
+    <row r="531" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H531" s="3"/>
     </row>
-    <row r="532" ht="15.75" customHeight="1">
+    <row r="532" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H532" s="3"/>
     </row>
-    <row r="533" ht="15.75" customHeight="1">
+    <row r="533" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H533" s="3"/>
     </row>
-    <row r="534" ht="15.75" customHeight="1">
+    <row r="534" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H534" s="3"/>
     </row>
-    <row r="535" ht="15.75" customHeight="1">
+    <row r="535" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H535" s="3"/>
     </row>
-    <row r="536" ht="15.75" customHeight="1">
+    <row r="536" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H536" s="3"/>
     </row>
-    <row r="537" ht="15.75" customHeight="1">
+    <row r="537" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H537" s="3"/>
     </row>
-    <row r="538" ht="15.75" customHeight="1">
+    <row r="538" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H538" s="3"/>
     </row>
-    <row r="539" ht="15.75" customHeight="1">
+    <row r="539" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H539" s="3"/>
     </row>
-    <row r="540" ht="15.75" customHeight="1">
+    <row r="540" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H540" s="3"/>
     </row>
-    <row r="541" ht="15.75" customHeight="1">
+    <row r="541" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H541" s="3"/>
     </row>
-    <row r="542" ht="15.75" customHeight="1">
+    <row r="542" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H542" s="3"/>
     </row>
-    <row r="543" ht="15.75" customHeight="1">
+    <row r="543" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H543" s="3"/>
     </row>
-    <row r="544" ht="15.75" customHeight="1">
+    <row r="544" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H544" s="3"/>
     </row>
-    <row r="545" ht="15.75" customHeight="1">
+    <row r="545" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H545" s="3"/>
     </row>
-    <row r="546" ht="15.75" customHeight="1">
+    <row r="546" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H546" s="3"/>
     </row>
-    <row r="547" ht="15.75" customHeight="1">
+    <row r="547" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H547" s="3"/>
     </row>
-    <row r="548" ht="15.75" customHeight="1">
+    <row r="548" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H548" s="3"/>
     </row>
-    <row r="549" ht="15.75" customHeight="1">
+    <row r="549" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H549" s="3"/>
     </row>
-    <row r="550" ht="15.75" customHeight="1">
+    <row r="550" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H550" s="3"/>
     </row>
-    <row r="551" ht="15.75" customHeight="1">
+    <row r="551" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H551" s="3"/>
     </row>
-    <row r="552" ht="15.75" customHeight="1">
+    <row r="552" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H552" s="3"/>
     </row>
-    <row r="553" ht="15.75" customHeight="1">
+    <row r="553" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H553" s="3"/>
     </row>
-    <row r="554" ht="15.75" customHeight="1">
+    <row r="554" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H554" s="3"/>
     </row>
-    <row r="555" ht="15.75" customHeight="1">
+    <row r="555" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H555" s="3"/>
     </row>
-    <row r="556" ht="15.75" customHeight="1">
+    <row r="556" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H556" s="3"/>
     </row>
-    <row r="557" ht="15.75" customHeight="1">
+    <row r="557" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H557" s="3"/>
     </row>
-    <row r="558" ht="15.75" customHeight="1">
+    <row r="558" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H558" s="3"/>
     </row>
-    <row r="559" ht="15.75" customHeight="1">
+    <row r="559" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H559" s="3"/>
     </row>
-    <row r="560" ht="15.75" customHeight="1">
+    <row r="560" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H560" s="3"/>
     </row>
-    <row r="561" ht="15.75" customHeight="1">
+    <row r="561" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H561" s="3"/>
     </row>
-    <row r="562" ht="15.75" customHeight="1">
+    <row r="562" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H562" s="3"/>
     </row>
-    <row r="563" ht="15.75" customHeight="1">
+    <row r="563" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H563" s="3"/>
     </row>
-    <row r="564" ht="15.75" customHeight="1">
+    <row r="564" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H564" s="3"/>
     </row>
-    <row r="565" ht="15.75" customHeight="1">
+    <row r="565" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H565" s="3"/>
     </row>
-    <row r="566" ht="15.75" customHeight="1">
+    <row r="566" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H566" s="3"/>
     </row>
-    <row r="567" ht="15.75" customHeight="1">
+    <row r="567" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H567" s="3"/>
     </row>
-    <row r="568" ht="15.75" customHeight="1">
+    <row r="568" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H568" s="3"/>
     </row>
-    <row r="569" ht="15.75" customHeight="1">
+    <row r="569" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H569" s="3"/>
     </row>
-    <row r="570" ht="15.75" customHeight="1">
+    <row r="570" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H570" s="3"/>
     </row>
-    <row r="571" ht="15.75" customHeight="1">
+    <row r="571" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H571" s="3"/>
     </row>
-    <row r="572" ht="15.75" customHeight="1">
+    <row r="572" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H572" s="3"/>
     </row>
-    <row r="573" ht="15.75" customHeight="1">
+    <row r="573" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H573" s="3"/>
     </row>
-    <row r="574" ht="15.75" customHeight="1">
+    <row r="574" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H574" s="3"/>
     </row>
-    <row r="575" ht="15.75" customHeight="1">
+    <row r="575" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H575" s="3"/>
     </row>
-    <row r="576" ht="15.75" customHeight="1">
+    <row r="576" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H576" s="3"/>
     </row>
-    <row r="577" ht="15.75" customHeight="1">
+    <row r="577" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H577" s="3"/>
     </row>
-    <row r="578" ht="15.75" customHeight="1">
+    <row r="578" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H578" s="3"/>
     </row>
-    <row r="579" ht="15.75" customHeight="1">
+    <row r="579" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H579" s="3"/>
     </row>
-    <row r="580" ht="15.75" customHeight="1">
+    <row r="580" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H580" s="3"/>
     </row>
-    <row r="581" ht="15.75" customHeight="1">
+    <row r="581" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H581" s="3"/>
     </row>
-    <row r="582" ht="15.75" customHeight="1">
+    <row r="582" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H582" s="3"/>
     </row>
-    <row r="583" ht="15.75" customHeight="1">
+    <row r="583" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H583" s="3"/>
     </row>
-    <row r="584" ht="15.75" customHeight="1">
+    <row r="584" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H584" s="3"/>
     </row>
-    <row r="585" ht="15.75" customHeight="1">
+    <row r="585" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H585" s="3"/>
     </row>
-    <row r="586" ht="15.75" customHeight="1">
+    <row r="586" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H586" s="3"/>
     </row>
-    <row r="587" ht="15.75" customHeight="1">
+    <row r="587" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H587" s="3"/>
     </row>
-    <row r="588" ht="15.75" customHeight="1">
+    <row r="588" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H588" s="3"/>
     </row>
-    <row r="589" ht="15.75" customHeight="1">
+    <row r="589" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H589" s="3"/>
     </row>
-    <row r="590" ht="15.75" customHeight="1">
+    <row r="590" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H590" s="3"/>
     </row>
-    <row r="591" ht="15.75" customHeight="1">
+    <row r="591" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H591" s="3"/>
     </row>
-    <row r="592" ht="15.75" customHeight="1">
+    <row r="592" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H592" s="3"/>
     </row>
-    <row r="593" ht="15.75" customHeight="1">
+    <row r="593" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H593" s="3"/>
     </row>
-    <row r="594" ht="15.75" customHeight="1">
+    <row r="594" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H594" s="3"/>
     </row>
-    <row r="595" ht="15.75" customHeight="1">
+    <row r="595" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H595" s="3"/>
     </row>
-    <row r="596" ht="15.75" customHeight="1">
+    <row r="596" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H596" s="3"/>
     </row>
-    <row r="597" ht="15.75" customHeight="1">
+    <row r="597" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H597" s="3"/>
     </row>
-    <row r="598" ht="15.75" customHeight="1">
+    <row r="598" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H598" s="3"/>
     </row>
-    <row r="599" ht="15.75" customHeight="1">
+    <row r="599" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H599" s="3"/>
     </row>
-    <row r="600" ht="15.75" customHeight="1">
+    <row r="600" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H600" s="3"/>
     </row>
-    <row r="601" ht="15.75" customHeight="1">
+    <row r="601" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H601" s="3"/>
     </row>
-    <row r="602" ht="15.75" customHeight="1">
+    <row r="602" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H602" s="3"/>
     </row>
-    <row r="603" ht="15.75" customHeight="1">
+    <row r="603" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H603" s="3"/>
     </row>
-    <row r="604" ht="15.75" customHeight="1">
+    <row r="604" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H604" s="3"/>
     </row>
-    <row r="605" ht="15.75" customHeight="1">
+    <row r="605" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H605" s="3"/>
     </row>
-    <row r="606" ht="15.75" customHeight="1">
+    <row r="606" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H606" s="3"/>
     </row>
-    <row r="607" ht="15.75" customHeight="1">
+    <row r="607" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H607" s="3"/>
     </row>
-    <row r="608" ht="15.75" customHeight="1">
+    <row r="608" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H608" s="3"/>
     </row>
-    <row r="609" ht="15.75" customHeight="1">
+    <row r="609" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H609" s="3"/>
     </row>
-    <row r="610" ht="15.75" customHeight="1">
+    <row r="610" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H610" s="3"/>
     </row>
-    <row r="611" ht="15.75" customHeight="1">
+    <row r="611" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H611" s="3"/>
     </row>
-    <row r="612" ht="15.75" customHeight="1">
+    <row r="612" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H612" s="3"/>
     </row>
-    <row r="613" ht="15.75" customHeight="1">
+    <row r="613" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H613" s="3"/>
     </row>
-    <row r="614" ht="15.75" customHeight="1">
+    <row r="614" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H614" s="3"/>
     </row>
-    <row r="615" ht="15.75" customHeight="1">
+    <row r="615" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H615" s="3"/>
     </row>
-    <row r="616" ht="15.75" customHeight="1">
+    <row r="616" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H616" s="3"/>
     </row>
-    <row r="617" ht="15.75" customHeight="1">
+    <row r="617" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H617" s="3"/>
     </row>
-    <row r="618" ht="15.75" customHeight="1">
+    <row r="618" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H618" s="3"/>
     </row>
-    <row r="619" ht="15.75" customHeight="1">
+    <row r="619" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H619" s="3"/>
     </row>
-    <row r="620" ht="15.75" customHeight="1">
+    <row r="620" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H620" s="3"/>
     </row>
-    <row r="621" ht="15.75" customHeight="1">
+    <row r="621" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H621" s="3"/>
     </row>
-    <row r="622" ht="15.75" customHeight="1">
+    <row r="622" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H622" s="3"/>
     </row>
-    <row r="623" ht="15.75" customHeight="1">
+    <row r="623" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H623" s="3"/>
     </row>
-    <row r="624" ht="15.75" customHeight="1">
+    <row r="624" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H624" s="3"/>
     </row>
-    <row r="625" ht="15.75" customHeight="1">
+    <row r="625" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H625" s="3"/>
     </row>
-    <row r="626" ht="15.75" customHeight="1">
+    <row r="626" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H626" s="3"/>
     </row>
-    <row r="627" ht="15.75" customHeight="1">
+    <row r="627" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H627" s="3"/>
     </row>
-    <row r="628" ht="15.75" customHeight="1">
+    <row r="628" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H628" s="3"/>
     </row>
-    <row r="629" ht="15.75" customHeight="1">
+    <row r="629" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H629" s="3"/>
     </row>
-    <row r="630" ht="15.75" customHeight="1">
+    <row r="630" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H630" s="3"/>
     </row>
-    <row r="631" ht="15.75" customHeight="1">
+    <row r="631" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H631" s="3"/>
     </row>
-    <row r="632" ht="15.75" customHeight="1">
+    <row r="632" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H632" s="3"/>
     </row>
-    <row r="633" ht="15.75" customHeight="1">
+    <row r="633" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H633" s="3"/>
     </row>
-    <row r="634" ht="15.75" customHeight="1">
+    <row r="634" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H634" s="3"/>
     </row>
-    <row r="635" ht="15.75" customHeight="1">
+    <row r="635" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H635" s="3"/>
     </row>
-    <row r="636" ht="15.75" customHeight="1">
+    <row r="636" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H636" s="3"/>
     </row>
-    <row r="637" ht="15.75" customHeight="1">
+    <row r="637" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H637" s="3"/>
     </row>
-    <row r="638" ht="15.75" customHeight="1">
+    <row r="638" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H638" s="3"/>
     </row>
-    <row r="639" ht="15.75" customHeight="1">
+    <row r="639" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H639" s="3"/>
     </row>
-    <row r="640" ht="15.75" customHeight="1">
+    <row r="640" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H640" s="3"/>
     </row>
-    <row r="641" ht="15.75" customHeight="1">
+    <row r="641" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H641" s="3"/>
     </row>
-    <row r="642" ht="15.75" customHeight="1">
+    <row r="642" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H642" s="3"/>
     </row>
-    <row r="643" ht="15.75" customHeight="1">
+    <row r="643" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H643" s="3"/>
     </row>
-    <row r="644" ht="15.75" customHeight="1">
+    <row r="644" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H644" s="3"/>
     </row>
-    <row r="645" ht="15.75" customHeight="1">
+    <row r="645" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H645" s="3"/>
     </row>
-    <row r="646" ht="15.75" customHeight="1">
+    <row r="646" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H646" s="3"/>
     </row>
-    <row r="647" ht="15.75" customHeight="1">
+    <row r="647" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H647" s="3"/>
     </row>
-    <row r="648" ht="15.75" customHeight="1">
+    <row r="648" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H648" s="3"/>
     </row>
-    <row r="649" ht="15.75" customHeight="1">
+    <row r="649" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H649" s="3"/>
     </row>
-    <row r="650" ht="15.75" customHeight="1">
+    <row r="650" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H650" s="3"/>
     </row>
-    <row r="651" ht="15.75" customHeight="1">
+    <row r="651" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H651" s="3"/>
     </row>
-    <row r="652" ht="15.75" customHeight="1">
+    <row r="652" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H652" s="3"/>
     </row>
-    <row r="653" ht="15.75" customHeight="1">
+    <row r="653" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H653" s="3"/>
     </row>
-    <row r="654" ht="15.75" customHeight="1">
+    <row r="654" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H654" s="3"/>
     </row>
-    <row r="655" ht="15.75" customHeight="1">
+    <row r="655" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H655" s="3"/>
     </row>
-    <row r="656" ht="15.75" customHeight="1">
+    <row r="656" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H656" s="3"/>
     </row>
-    <row r="657" ht="15.75" customHeight="1">
+    <row r="657" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H657" s="3"/>
     </row>
-    <row r="658" ht="15.75" customHeight="1">
+    <row r="658" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H658" s="3"/>
     </row>
-    <row r="659" ht="15.75" customHeight="1">
+    <row r="659" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H659" s="3"/>
     </row>
-    <row r="660" ht="15.75" customHeight="1">
+    <row r="660" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H660" s="3"/>
     </row>
-    <row r="661" ht="15.75" customHeight="1">
+    <row r="661" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H661" s="3"/>
     </row>
-    <row r="662" ht="15.75" customHeight="1">
+    <row r="662" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H662" s="3"/>
     </row>
-    <row r="663" ht="15.75" customHeight="1">
+    <row r="663" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H663" s="3"/>
     </row>
-    <row r="664" ht="15.75" customHeight="1">
+    <row r="664" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H664" s="3"/>
     </row>
-    <row r="665" ht="15.75" customHeight="1">
+    <row r="665" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H665" s="3"/>
     </row>
-    <row r="666" ht="15.75" customHeight="1">
+    <row r="666" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H666" s="3"/>
     </row>
-    <row r="667" ht="15.75" customHeight="1">
+    <row r="667" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H667" s="3"/>
     </row>
-    <row r="668" ht="15.75" customHeight="1">
+    <row r="668" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H668" s="3"/>
     </row>
-    <row r="669" ht="15.75" customHeight="1">
+    <row r="669" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H669" s="3"/>
     </row>
-    <row r="670" ht="15.75" customHeight="1">
+    <row r="670" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H670" s="3"/>
     </row>
-    <row r="671" ht="15.75" customHeight="1">
+    <row r="671" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H671" s="3"/>
     </row>
-    <row r="672" ht="15.75" customHeight="1">
+    <row r="672" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H672" s="3"/>
     </row>
-    <row r="673" ht="15.75" customHeight="1">
+    <row r="673" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H673" s="3"/>
     </row>
-    <row r="674" ht="15.75" customHeight="1">
+    <row r="674" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H674" s="3"/>
     </row>
-    <row r="675" ht="15.75" customHeight="1">
+    <row r="675" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H675" s="3"/>
     </row>
-    <row r="676" ht="15.75" customHeight="1">
+    <row r="676" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H676" s="3"/>
     </row>
-    <row r="677" ht="15.75" customHeight="1">
+    <row r="677" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H677" s="3"/>
     </row>
-    <row r="678" ht="15.75" customHeight="1">
+    <row r="678" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H678" s="3"/>
     </row>
-    <row r="679" ht="15.75" customHeight="1">
+    <row r="679" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H679" s="3"/>
     </row>
-    <row r="680" ht="15.75" customHeight="1">
+    <row r="680" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H680" s="3"/>
     </row>
-    <row r="681" ht="15.75" customHeight="1">
+    <row r="681" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H681" s="3"/>
     </row>
-    <row r="682" ht="15.75" customHeight="1">
+    <row r="682" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H682" s="3"/>
     </row>
-    <row r="683" ht="15.75" customHeight="1">
+    <row r="683" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H683" s="3"/>
     </row>
-    <row r="684" ht="15.75" customHeight="1">
+    <row r="684" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H684" s="3"/>
     </row>
-    <row r="685" ht="15.75" customHeight="1">
+    <row r="685" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H685" s="3"/>
     </row>
-    <row r="686" ht="15.75" customHeight="1">
+    <row r="686" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H686" s="3"/>
     </row>
-    <row r="687" ht="15.75" customHeight="1">
+    <row r="687" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H687" s="3"/>
     </row>
-    <row r="688" ht="15.75" customHeight="1">
+    <row r="688" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H688" s="3"/>
     </row>
-    <row r="689" ht="15.75" customHeight="1">
+    <row r="689" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H689" s="3"/>
     </row>
-    <row r="690" ht="15.75" customHeight="1">
+    <row r="690" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H690" s="3"/>
     </row>
-    <row r="691" ht="15.75" customHeight="1">
+    <row r="691" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H691" s="3"/>
     </row>
-    <row r="692" ht="15.75" customHeight="1">
+    <row r="692" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H692" s="3"/>
     </row>
-    <row r="693" ht="15.75" customHeight="1">
+    <row r="693" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H693" s="3"/>
     </row>
-    <row r="694" ht="15.75" customHeight="1">
+    <row r="694" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H694" s="3"/>
     </row>
-    <row r="695" ht="15.75" customHeight="1">
+    <row r="695" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H695" s="3"/>
     </row>
-    <row r="696" ht="15.75" customHeight="1">
+    <row r="696" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H696" s="3"/>
     </row>
-    <row r="697" ht="15.75" customHeight="1">
+    <row r="697" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H697" s="3"/>
     </row>
-    <row r="698" ht="15.75" customHeight="1">
+    <row r="698" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H698" s="3"/>
     </row>
-    <row r="699" ht="15.75" customHeight="1">
+    <row r="699" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H699" s="3"/>
     </row>
-    <row r="700" ht="15.75" customHeight="1">
+    <row r="700" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H700" s="3"/>
     </row>
-    <row r="701" ht="15.75" customHeight="1">
+    <row r="701" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H701" s="3"/>
     </row>
-    <row r="702" ht="15.75" customHeight="1">
+    <row r="702" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H702" s="3"/>
     </row>
-    <row r="703" ht="15.75" customHeight="1">
+    <row r="703" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H703" s="3"/>
     </row>
-    <row r="704" ht="15.75" customHeight="1">
+    <row r="704" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H704" s="3"/>
     </row>
-    <row r="705" ht="15.75" customHeight="1">
+    <row r="705" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H705" s="3"/>
     </row>
-    <row r="706" ht="15.75" customHeight="1">
+    <row r="706" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H706" s="3"/>
     </row>
-    <row r="707" ht="15.75" customHeight="1">
+    <row r="707" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H707" s="3"/>
     </row>
-    <row r="708" ht="15.75" customHeight="1">
+    <row r="708" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H708" s="3"/>
     </row>
-    <row r="709" ht="15.75" customHeight="1">
+    <row r="709" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H709" s="3"/>
     </row>
-    <row r="710" ht="15.75" customHeight="1">
+    <row r="710" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H710" s="3"/>
     </row>
-    <row r="711" ht="15.75" customHeight="1">
+    <row r="711" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H711" s="3"/>
     </row>
-    <row r="712" ht="15.75" customHeight="1">
+    <row r="712" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H712" s="3"/>
     </row>
-    <row r="713" ht="15.75" customHeight="1">
+    <row r="713" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H713" s="3"/>
     </row>
-    <row r="714" ht="15.75" customHeight="1">
+    <row r="714" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H714" s="3"/>
     </row>
-    <row r="715" ht="15.75" customHeight="1">
+    <row r="715" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H715" s="3"/>
     </row>
-    <row r="716" ht="15.75" customHeight="1">
+    <row r="716" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H716" s="3"/>
     </row>
-    <row r="717" ht="15.75" customHeight="1">
+    <row r="717" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H717" s="3"/>
     </row>
-    <row r="718" ht="15.75" customHeight="1">
+    <row r="718" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H718" s="3"/>
     </row>
-    <row r="719" ht="15.75" customHeight="1">
+    <row r="719" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H719" s="3"/>
     </row>
-    <row r="720" ht="15.75" customHeight="1">
+    <row r="720" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H720" s="3"/>
     </row>
-    <row r="721" ht="15.75" customHeight="1">
+    <row r="721" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H721" s="3"/>
     </row>
-    <row r="722" ht="15.75" customHeight="1">
+    <row r="722" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H722" s="3"/>
     </row>
-    <row r="723" ht="15.75" customHeight="1">
+    <row r="723" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H723" s="3"/>
     </row>
-    <row r="724" ht="15.75" customHeight="1">
+    <row r="724" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H724" s="3"/>
     </row>
-    <row r="725" ht="15.75" customHeight="1">
+    <row r="725" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H725" s="3"/>
     </row>
-    <row r="726" ht="15.75" customHeight="1">
+    <row r="726" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H726" s="3"/>
     </row>
-    <row r="727" ht="15.75" customHeight="1">
+    <row r="727" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H727" s="3"/>
     </row>
-    <row r="728" ht="15.75" customHeight="1">
+    <row r="728" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H728" s="3"/>
     </row>
-    <row r="729" ht="15.75" customHeight="1">
+    <row r="729" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H729" s="3"/>
     </row>
-    <row r="730" ht="15.75" customHeight="1">
+    <row r="730" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H730" s="3"/>
     </row>
-    <row r="731" ht="15.75" customHeight="1">
+    <row r="731" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H731" s="3"/>
     </row>
-    <row r="732" ht="15.75" customHeight="1">
+    <row r="732" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H732" s="3"/>
     </row>
-    <row r="733" ht="15.75" customHeight="1">
+    <row r="733" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H733" s="3"/>
     </row>
-    <row r="734" ht="15.75" customHeight="1">
+    <row r="734" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H734" s="3"/>
     </row>
-    <row r="735" ht="15.75" customHeight="1">
+    <row r="735" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H735" s="3"/>
     </row>
-    <row r="736" ht="15.75" customHeight="1">
+    <row r="736" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H736" s="3"/>
     </row>
-    <row r="737" ht="15.75" customHeight="1">
+    <row r="737" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H737" s="3"/>
     </row>
-    <row r="738" ht="15.75" customHeight="1">
+    <row r="738" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H738" s="3"/>
     </row>
-    <row r="739" ht="15.75" customHeight="1">
+    <row r="739" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H739" s="3"/>
     </row>
-    <row r="740" ht="15.75" customHeight="1">
+    <row r="740" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H740" s="3"/>
     </row>
-    <row r="741" ht="15.75" customHeight="1">
+    <row r="741" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H741" s="3"/>
     </row>
-    <row r="742" ht="15.75" customHeight="1">
+    <row r="742" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H742" s="3"/>
     </row>
-    <row r="743" ht="15.75" customHeight="1">
+    <row r="743" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H743" s="3"/>
     </row>
-    <row r="744" ht="15.75" customHeight="1">
+    <row r="744" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H744" s="3"/>
     </row>
-    <row r="745" ht="15.75" customHeight="1">
+    <row r="745" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H745" s="3"/>
     </row>
-    <row r="746" ht="15.75" customHeight="1">
+    <row r="746" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H746" s="3"/>
     </row>
-    <row r="747" ht="15.75" customHeight="1">
+    <row r="747" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H747" s="3"/>
     </row>
-    <row r="748" ht="15.75" customHeight="1">
+    <row r="748" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H748" s="3"/>
     </row>
-    <row r="749" ht="15.75" customHeight="1">
+    <row r="749" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H749" s="3"/>
     </row>
-    <row r="750" ht="15.75" customHeight="1">
+    <row r="750" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H750" s="3"/>
     </row>
-    <row r="751" ht="15.75" customHeight="1">
+    <row r="751" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H751" s="3"/>
     </row>
-    <row r="752" ht="15.75" customHeight="1">
+    <row r="752" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H752" s="3"/>
     </row>
-    <row r="753" ht="15.75" customHeight="1">
+    <row r="753" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H753" s="3"/>
     </row>
-    <row r="754" ht="15.75" customHeight="1">
+    <row r="754" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H754" s="3"/>
     </row>
-    <row r="755" ht="15.75" customHeight="1">
+    <row r="755" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H755" s="3"/>
     </row>
-    <row r="756" ht="15.75" customHeight="1">
+    <row r="756" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H756" s="3"/>
     </row>
-    <row r="757" ht="15.75" customHeight="1">
+    <row r="757" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H757" s="3"/>
     </row>
-    <row r="758" ht="15.75" customHeight="1">
+    <row r="758" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H758" s="3"/>
     </row>
-    <row r="759" ht="15.75" customHeight="1">
+    <row r="759" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H759" s="3"/>
     </row>
-    <row r="760" ht="15.75" customHeight="1">
+    <row r="760" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H760" s="3"/>
     </row>
-    <row r="761" ht="15.75" customHeight="1">
+    <row r="761" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H761" s="3"/>
     </row>
-    <row r="762" ht="15.75" customHeight="1">
+    <row r="762" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H762" s="3"/>
     </row>
-    <row r="763" ht="15.75" customHeight="1">
+    <row r="763" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H763" s="3"/>
     </row>
-    <row r="764" ht="15.75" customHeight="1">
+    <row r="764" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H764" s="3"/>
     </row>
-    <row r="765" ht="15.75" customHeight="1">
+    <row r="765" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H765" s="3"/>
     </row>
-    <row r="766" ht="15.75" customHeight="1">
+    <row r="766" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H766" s="3"/>
     </row>
-    <row r="767" ht="15.75" customHeight="1">
+    <row r="767" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H767" s="3"/>
     </row>
-    <row r="768" ht="15.75" customHeight="1">
+    <row r="768" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H768" s="3"/>
     </row>
-    <row r="769" ht="15.75" customHeight="1">
+    <row r="769" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H769" s="3"/>
     </row>
-    <row r="770" ht="15.75" customHeight="1">
+    <row r="770" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H770" s="3"/>
     </row>
-    <row r="771" ht="15.75" customHeight="1">
+    <row r="771" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H771" s="3"/>
     </row>
-    <row r="772" ht="15.75" customHeight="1">
+    <row r="772" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H772" s="3"/>
     </row>
-    <row r="773" ht="15.75" customHeight="1">
+    <row r="773" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H773" s="3"/>
     </row>
-    <row r="774" ht="15.75" customHeight="1">
+    <row r="774" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H774" s="3"/>
     </row>
-    <row r="775" ht="15.75" customHeight="1">
+    <row r="775" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H775" s="3"/>
     </row>
-    <row r="776" ht="15.75" customHeight="1">
+    <row r="776" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H776" s="3"/>
     </row>
-    <row r="777" ht="15.75" customHeight="1">
+    <row r="777" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H777" s="3"/>
     </row>
-    <row r="778" ht="15.75" customHeight="1">
+    <row r="778" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H778" s="3"/>
     </row>
-    <row r="779" ht="15.75" customHeight="1">
+    <row r="779" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H779" s="3"/>
     </row>
-    <row r="780" ht="15.75" customHeight="1">
+    <row r="780" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H780" s="3"/>
     </row>
-    <row r="781" ht="15.75" customHeight="1">
+    <row r="781" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H781" s="3"/>
     </row>
-    <row r="782" ht="15.75" customHeight="1">
+    <row r="782" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H782" s="3"/>
     </row>
-    <row r="783" ht="15.75" customHeight="1">
+    <row r="783" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H783" s="3"/>
     </row>
-    <row r="784" ht="15.75" customHeight="1">
+    <row r="784" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H784" s="3"/>
     </row>
-    <row r="785" ht="15.75" customHeight="1">
+    <row r="785" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H785" s="3"/>
     </row>
-    <row r="786" ht="15.75" customHeight="1">
+    <row r="786" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H786" s="3"/>
     </row>
-    <row r="787" ht="15.75" customHeight="1">
+    <row r="787" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H787" s="3"/>
     </row>
-    <row r="788" ht="15.75" customHeight="1">
+    <row r="788" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H788" s="3"/>
     </row>
-    <row r="789" ht="15.75" customHeight="1">
+    <row r="789" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H789" s="3"/>
     </row>
-    <row r="790" ht="15.75" customHeight="1">
+    <row r="790" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H790" s="3"/>
     </row>
-    <row r="791" ht="15.75" customHeight="1">
+    <row r="791" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H791" s="3"/>
     </row>
-    <row r="792" ht="15.75" customHeight="1">
+    <row r="792" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H792" s="3"/>
     </row>
-    <row r="793" ht="15.75" customHeight="1">
+    <row r="793" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H793" s="3"/>
     </row>
-    <row r="794" ht="15.75" customHeight="1">
+    <row r="794" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H794" s="3"/>
     </row>
-    <row r="795" ht="15.75" customHeight="1">
+    <row r="795" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H795" s="3"/>
     </row>
-    <row r="796" ht="15.75" customHeight="1">
+    <row r="796" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H796" s="3"/>
     </row>
-    <row r="797" ht="15.75" customHeight="1">
+    <row r="797" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H797" s="3"/>
     </row>
-    <row r="798" ht="15.75" customHeight="1">
+    <row r="798" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H798" s="3"/>
     </row>
-    <row r="799" ht="15.75" customHeight="1">
+    <row r="799" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H799" s="3"/>
     </row>
-    <row r="800" ht="15.75" customHeight="1">
+    <row r="800" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H800" s="3"/>
     </row>
-    <row r="801" ht="15.75" customHeight="1">
+    <row r="801" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H801" s="3"/>
     </row>
-    <row r="802" ht="15.75" customHeight="1">
+    <row r="802" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H802" s="3"/>
     </row>
-    <row r="803" ht="15.75" customHeight="1">
+    <row r="803" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H803" s="3"/>
     </row>
-    <row r="804" ht="15.75" customHeight="1">
+    <row r="804" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H804" s="3"/>
     </row>
-    <row r="805" ht="15.75" customHeight="1">
+    <row r="805" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H805" s="3"/>
     </row>
-    <row r="806" ht="15.75" customHeight="1">
+    <row r="806" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H806" s="3"/>
     </row>
-    <row r="807" ht="15.75" customHeight="1">
+    <row r="807" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H807" s="3"/>
     </row>
-    <row r="808" ht="15.75" customHeight="1">
+    <row r="808" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H808" s="3"/>
     </row>
-    <row r="809" ht="15.75" customHeight="1">
+    <row r="809" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H809" s="3"/>
     </row>
-    <row r="810" ht="15.75" customHeight="1">
+    <row r="810" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H810" s="3"/>
     </row>
-    <row r="811" ht="15.75" customHeight="1">
+    <row r="811" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H811" s="3"/>
     </row>
-    <row r="812" ht="15.75" customHeight="1">
+    <row r="812" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H812" s="3"/>
     </row>
-    <row r="813" ht="15.75" customHeight="1">
+    <row r="813" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H813" s="3"/>
     </row>
-    <row r="814" ht="15.75" customHeight="1">
+    <row r="814" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H814" s="3"/>
     </row>
-    <row r="815" ht="15.75" customHeight="1">
+    <row r="815" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H815" s="3"/>
     </row>
-    <row r="816" ht="15.75" customHeight="1">
+    <row r="816" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H816" s="3"/>
     </row>
-    <row r="817" ht="15.75" customHeight="1">
+    <row r="817" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H817" s="3"/>
     </row>
-    <row r="818" ht="15.75" customHeight="1">
+    <row r="818" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H818" s="3"/>
     </row>
-    <row r="819" ht="15.75" customHeight="1">
+    <row r="819" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H819" s="3"/>
     </row>
-    <row r="820" ht="15.75" customHeight="1">
+    <row r="820" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H820" s="3"/>
     </row>
-    <row r="821" ht="15.75" customHeight="1">
+    <row r="821" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H821" s="3"/>
     </row>
-    <row r="822" ht="15.75" customHeight="1">
+    <row r="822" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H822" s="3"/>
     </row>
-    <row r="823" ht="15.75" customHeight="1">
+    <row r="823" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H823" s="3"/>
     </row>
-    <row r="824" ht="15.75" customHeight="1">
+    <row r="824" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H824" s="3"/>
     </row>
-    <row r="825" ht="15.75" customHeight="1">
+    <row r="825" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H825" s="3"/>
     </row>
-    <row r="826" ht="15.75" customHeight="1">
+    <row r="826" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H826" s="3"/>
     </row>
-    <row r="827" ht="15.75" customHeight="1">
+    <row r="827" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H827" s="3"/>
     </row>
-    <row r="828" ht="15.75" customHeight="1">
+    <row r="828" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H828" s="3"/>
     </row>
-    <row r="829" ht="15.75" customHeight="1">
+    <row r="829" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H829" s="3"/>
     </row>
-    <row r="830" ht="15.75" customHeight="1">
+    <row r="830" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H830" s="3"/>
     </row>
-    <row r="831" ht="15.75" customHeight="1">
+    <row r="831" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H831" s="3"/>
     </row>
-    <row r="832" ht="15.75" customHeight="1">
+    <row r="832" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H832" s="3"/>
     </row>
-    <row r="833" ht="15.75" customHeight="1">
+    <row r="833" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H833" s="3"/>
     </row>
-    <row r="834" ht="15.75" customHeight="1">
+    <row r="834" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H834" s="3"/>
     </row>
-    <row r="835" ht="15.75" customHeight="1">
+    <row r="835" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H835" s="3"/>
     </row>
-    <row r="836" ht="15.75" customHeight="1">
+    <row r="836" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H836" s="3"/>
     </row>
-    <row r="837" ht="15.75" customHeight="1">
+    <row r="837" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H837" s="3"/>
     </row>
-    <row r="838" ht="15.75" customHeight="1">
+    <row r="838" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H838" s="3"/>
     </row>
-    <row r="839" ht="15.75" customHeight="1">
+    <row r="839" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H839" s="3"/>
     </row>
-    <row r="840" ht="15.75" customHeight="1">
+    <row r="840" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H840" s="3"/>
     </row>
-    <row r="841" ht="15.75" customHeight="1">
+    <row r="841" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H841" s="3"/>
     </row>
-    <row r="842" ht="15.75" customHeight="1">
+    <row r="842" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H842" s="3"/>
     </row>
-    <row r="843" ht="15.75" customHeight="1">
+    <row r="843" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H843" s="3"/>
     </row>
-    <row r="844" ht="15.75" customHeight="1">
+    <row r="844" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H844" s="3"/>
     </row>
-    <row r="845" ht="15.75" customHeight="1">
+    <row r="845" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H845" s="3"/>
     </row>
-    <row r="846" ht="15.75" customHeight="1">
+    <row r="846" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H846" s="3"/>
     </row>
-    <row r="847" ht="15.75" customHeight="1">
+    <row r="847" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H847" s="3"/>
     </row>
-    <row r="848" ht="15.75" customHeight="1">
+    <row r="848" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H848" s="3"/>
     </row>
-    <row r="849" ht="15.75" customHeight="1">
+    <row r="849" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H849" s="3"/>
     </row>
-    <row r="850" ht="15.75" customHeight="1">
+    <row r="850" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H850" s="3"/>
     </row>
-    <row r="851" ht="15.75" customHeight="1">
+    <row r="851" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H851" s="3"/>
     </row>
-    <row r="852" ht="15.75" customHeight="1">
+    <row r="852" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H852" s="3"/>
     </row>
-    <row r="853" ht="15.75" customHeight="1">
+    <row r="853" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H853" s="3"/>
     </row>
-    <row r="854" ht="15.75" customHeight="1">
+    <row r="854" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H854" s="3"/>
     </row>
-    <row r="855" ht="15.75" customHeight="1">
+    <row r="855" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H855" s="3"/>
     </row>
-    <row r="856" ht="15.75" customHeight="1">
+    <row r="856" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H856" s="3"/>
     </row>
-    <row r="857" ht="15.75" customHeight="1">
+    <row r="857" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H857" s="3"/>
     </row>
-    <row r="858" ht="15.75" customHeight="1">
+    <row r="858" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H858" s="3"/>
     </row>
-    <row r="859" ht="15.75" customHeight="1">
+    <row r="859" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H859" s="3"/>
     </row>
-    <row r="860" ht="15.75" customHeight="1">
+    <row r="860" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H860" s="3"/>
     </row>
-    <row r="861" ht="15.75" customHeight="1">
+    <row r="861" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H861" s="3"/>
     </row>
-    <row r="862" ht="15.75" customHeight="1">
+    <row r="862" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H862" s="3"/>
     </row>
-    <row r="863" ht="15.75" customHeight="1">
+    <row r="863" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H863" s="3"/>
     </row>
-    <row r="864" ht="15.75" customHeight="1">
+    <row r="864" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H864" s="3"/>
     </row>
-    <row r="865" ht="15.75" customHeight="1">
+    <row r="865" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H865" s="3"/>
     </row>
-    <row r="866" ht="15.75" customHeight="1">
+    <row r="866" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H866" s="3"/>
     </row>
-    <row r="867" ht="15.75" customHeight="1">
+    <row r="867" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H867" s="3"/>
     </row>
-    <row r="868" ht="15.75" customHeight="1">
+    <row r="868" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H868" s="3"/>
     </row>
-    <row r="869" ht="15.75" customHeight="1">
+    <row r="869" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H869" s="3"/>
     </row>
-    <row r="870" ht="15.75" customHeight="1">
+    <row r="870" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H870" s="3"/>
     </row>
-    <row r="871" ht="15.75" customHeight="1">
+    <row r="871" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H871" s="3"/>
     </row>
-    <row r="872" ht="15.75" customHeight="1">
+    <row r="872" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H872" s="3"/>
     </row>
-    <row r="873" ht="15.75" customHeight="1">
+    <row r="873" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H873" s="3"/>
     </row>
-    <row r="874" ht="15.75" customHeight="1">
+    <row r="874" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H874" s="3"/>
     </row>
-    <row r="875" ht="15.75" customHeight="1">
+    <row r="875" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H875" s="3"/>
     </row>
-    <row r="876" ht="15.75" customHeight="1">
+    <row r="876" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H876" s="3"/>
     </row>
-    <row r="877" ht="15.75" customHeight="1">
+    <row r="877" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H877" s="3"/>
     </row>
-    <row r="878" ht="15.75" customHeight="1">
+    <row r="878" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H878" s="3"/>
     </row>
-    <row r="879" ht="15.75" customHeight="1">
+    <row r="879" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H879" s="3"/>
     </row>
-    <row r="880" ht="15.75" customHeight="1">
+    <row r="880" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H880" s="3"/>
     </row>
-    <row r="881" ht="15.75" customHeight="1">
+    <row r="881" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H881" s="3"/>
     </row>
-    <row r="882" ht="15.75" customHeight="1">
+    <row r="882" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H882" s="3"/>
     </row>
-    <row r="883" ht="15.75" customHeight="1">
+    <row r="883" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H883" s="3"/>
     </row>
-    <row r="884" ht="15.75" customHeight="1">
+    <row r="884" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H884" s="3"/>
     </row>
-    <row r="885" ht="15.75" customHeight="1">
+    <row r="885" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H885" s="3"/>
     </row>
-    <row r="886" ht="15.75" customHeight="1">
+    <row r="886" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H886" s="3"/>
     </row>
-    <row r="887" ht="15.75" customHeight="1">
+    <row r="887" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H887" s="3"/>
     </row>
-    <row r="888" ht="15.75" customHeight="1">
+    <row r="888" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H888" s="3"/>
     </row>
-    <row r="889" ht="15.75" customHeight="1">
+    <row r="889" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H889" s="3"/>
     </row>
-    <row r="890" ht="15.75" customHeight="1">
+    <row r="890" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H890" s="3"/>
     </row>
-    <row r="891" ht="15.75" customHeight="1">
+    <row r="891" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H891" s="3"/>
     </row>
-    <row r="892" ht="15.75" customHeight="1">
+    <row r="892" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H892" s="3"/>
     </row>
-    <row r="893" ht="15.75" customHeight="1">
+    <row r="893" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H893" s="3"/>
     </row>
-    <row r="894" ht="15.75" customHeight="1">
+    <row r="894" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H894" s="3"/>
     </row>
-    <row r="895" ht="15.75" customHeight="1">
+    <row r="895" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H895" s="3"/>
     </row>
-    <row r="896" ht="15.75" customHeight="1">
+    <row r="896" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H896" s="3"/>
     </row>
-    <row r="897" ht="15.75" customHeight="1">
+    <row r="897" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H897" s="3"/>
     </row>
-    <row r="898" ht="15.75" customHeight="1">
+    <row r="898" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H898" s="3"/>
     </row>
-    <row r="899" ht="15.75" customHeight="1">
+    <row r="899" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H899" s="3"/>
     </row>
-    <row r="900" ht="15.75" customHeight="1">
+    <row r="900" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H900" s="3"/>
     </row>
-    <row r="901" ht="15.75" customHeight="1">
+    <row r="901" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H901" s="3"/>
     </row>
-    <row r="902" ht="15.75" customHeight="1">
+    <row r="902" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H902" s="3"/>
     </row>
-    <row r="903" ht="15.75" customHeight="1">
+    <row r="903" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H903" s="3"/>
     </row>
-    <row r="904" ht="15.75" customHeight="1">
+    <row r="904" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H904" s="3"/>
     </row>
-    <row r="905" ht="15.75" customHeight="1">
+    <row r="905" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H905" s="3"/>
     </row>
-    <row r="906" ht="15.75" customHeight="1">
+    <row r="906" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H906" s="3"/>
     </row>
-    <row r="907" ht="15.75" customHeight="1">
+    <row r="907" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H907" s="3"/>
     </row>
-    <row r="908" ht="15.75" customHeight="1">
+    <row r="908" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H908" s="3"/>
     </row>
-    <row r="909" ht="15.75" customHeight="1">
+    <row r="909" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H909" s="3"/>
     </row>
-    <row r="910" ht="15.75" customHeight="1">
+    <row r="910" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H910" s="3"/>
     </row>
-    <row r="911" ht="15.75" customHeight="1">
+    <row r="911" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H911" s="3"/>
     </row>
-    <row r="912" ht="15.75" customHeight="1">
+    <row r="912" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H912" s="3"/>
     </row>
-    <row r="913" ht="15.75" customHeight="1">
+    <row r="913" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H913" s="3"/>
     </row>
-    <row r="914" ht="15.75" customHeight="1">
+    <row r="914" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H914" s="3"/>
     </row>
-    <row r="915" ht="15.75" customHeight="1">
+    <row r="915" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H915" s="3"/>
     </row>
-    <row r="916" ht="15.75" customHeight="1">
+    <row r="916" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H916" s="3"/>
     </row>
-    <row r="917" ht="15.75" customHeight="1">
+    <row r="917" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H917" s="3"/>
     </row>
-    <row r="918" ht="15.75" customHeight="1">
+    <row r="918" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H918" s="3"/>
     </row>
-    <row r="919" ht="15.75" customHeight="1">
+    <row r="919" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H919" s="3"/>
     </row>
-    <row r="920" ht="15.75" customHeight="1">
+    <row r="920" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H920" s="3"/>
     </row>
-    <row r="921" ht="15.75" customHeight="1">
+    <row r="921" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H921" s="3"/>
     </row>
-    <row r="922" ht="15.75" customHeight="1">
+    <row r="922" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H922" s="3"/>
     </row>
-    <row r="923" ht="15.75" customHeight="1">
+    <row r="923" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H923" s="3"/>
     </row>
-    <row r="924" ht="15.75" customHeight="1">
+    <row r="924" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H924" s="3"/>
     </row>
-    <row r="925" ht="15.75" customHeight="1">
+    <row r="925" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H925" s="3"/>
     </row>
-    <row r="926" ht="15.75" customHeight="1">
+    <row r="926" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H926" s="3"/>
     </row>
-    <row r="927" ht="15.75" customHeight="1">
+    <row r="927" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H927" s="3"/>
     </row>
-    <row r="928" ht="15.75" customHeight="1">
+    <row r="928" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H928" s="3"/>
     </row>
-    <row r="929" ht="15.75" customHeight="1">
+    <row r="929" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H929" s="3"/>
     </row>
-    <row r="930" ht="15.75" customHeight="1">
+    <row r="930" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H930" s="3"/>
     </row>
-    <row r="931" ht="15.75" customHeight="1">
+    <row r="931" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H931" s="3"/>
     </row>
-    <row r="932" ht="15.75" customHeight="1">
+    <row r="932" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H932" s="3"/>
     </row>
-    <row r="933" ht="15.75" customHeight="1">
+    <row r="933" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H933" s="3"/>
     </row>
-    <row r="934" ht="15.75" customHeight="1">
+    <row r="934" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H934" s="3"/>
     </row>
-    <row r="935" ht="15.75" customHeight="1">
+    <row r="935" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H935" s="3"/>
     </row>
-    <row r="936" ht="15.75" customHeight="1">
+    <row r="936" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H936" s="3"/>
     </row>
-    <row r="937" ht="15.75" customHeight="1">
+    <row r="937" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H937" s="3"/>
     </row>
-    <row r="938" ht="15.75" customHeight="1">
+    <row r="938" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H938" s="3"/>
     </row>
-    <row r="939" ht="15.75" customHeight="1">
+    <row r="939" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H939" s="3"/>
     </row>
-    <row r="940" ht="15.75" customHeight="1">
+    <row r="940" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H940" s="3"/>
     </row>
-    <row r="941" ht="15.75" customHeight="1">
+    <row r="941" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H941" s="3"/>
     </row>
-    <row r="942" ht="15.75" customHeight="1">
+    <row r="942" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H942" s="3"/>
     </row>
-    <row r="943" ht="15.75" customHeight="1">
+    <row r="943" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H943" s="3"/>
     </row>
-    <row r="944" ht="15.75" customHeight="1">
+    <row r="944" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H944" s="3"/>
     </row>
-    <row r="945" ht="15.75" customHeight="1">
+    <row r="945" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H945" s="3"/>
     </row>
-    <row r="946" ht="15.75" customHeight="1">
+    <row r="946" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H946" s="3"/>
     </row>
-    <row r="947" ht="15.75" customHeight="1">
+    <row r="947" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H947" s="3"/>
     </row>
-    <row r="948" ht="15.75" customHeight="1">
+    <row r="948" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H948" s="3"/>
     </row>
-    <row r="949" ht="15.75" customHeight="1">
+    <row r="949" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H949" s="3"/>
     </row>
-    <row r="950" ht="15.75" customHeight="1">
+    <row r="950" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H950" s="3"/>
     </row>
-    <row r="951" ht="15.75" customHeight="1">
+    <row r="951" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H951" s="3"/>
     </row>
-    <row r="952" ht="15.75" customHeight="1">
+    <row r="952" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H952" s="3"/>
     </row>
-    <row r="953" ht="15.75" customHeight="1">
+    <row r="953" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H953" s="3"/>
     </row>
-    <row r="954" ht="15.75" customHeight="1">
+    <row r="954" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H954" s="3"/>
     </row>
-    <row r="955" ht="15.75" customHeight="1">
+    <row r="955" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H955" s="3"/>
     </row>
-    <row r="956" ht="15.75" customHeight="1">
+    <row r="956" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H956" s="3"/>
     </row>
-    <row r="957" ht="15.75" customHeight="1">
+    <row r="957" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H957" s="3"/>
     </row>
-    <row r="958" ht="15.75" customHeight="1">
+    <row r="958" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H958" s="3"/>
     </row>
-    <row r="959" ht="15.75" customHeight="1">
+    <row r="959" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H959" s="3"/>
     </row>
-    <row r="960" ht="15.75" customHeight="1">
+    <row r="960" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H960" s="3"/>
     </row>
-    <row r="961" ht="15.75" customHeight="1">
+    <row r="961" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H961" s="3"/>
     </row>
-    <row r="962" ht="15.75" customHeight="1">
+    <row r="962" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H962" s="3"/>
     </row>
-    <row r="963" ht="15.75" customHeight="1">
+    <row r="963" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H963" s="3"/>
     </row>
-    <row r="964" ht="15.75" customHeight="1">
+    <row r="964" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H964" s="3"/>
     </row>
-    <row r="965" ht="15.75" customHeight="1">
+    <row r="965" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H965" s="3"/>
     </row>
-    <row r="966" ht="15.75" customHeight="1">
+    <row r="966" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H966" s="3"/>
     </row>
-    <row r="967" ht="15.75" customHeight="1">
+    <row r="967" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H967" s="3"/>
     </row>
-    <row r="968" ht="15.75" customHeight="1">
+    <row r="968" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H968" s="3"/>
     </row>
-    <row r="969" ht="15.75" customHeight="1">
+    <row r="969" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H969" s="3"/>
     </row>
-    <row r="970" ht="15.75" customHeight="1">
+    <row r="970" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H970" s="3"/>
     </row>
-    <row r="971" ht="15.75" customHeight="1">
+    <row r="971" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H971" s="3"/>
     </row>
-    <row r="972" ht="15.75" customHeight="1">
+    <row r="972" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H972" s="3"/>
     </row>
-    <row r="973" ht="15.75" customHeight="1">
+    <row r="973" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H973" s="3"/>
     </row>
-    <row r="974" ht="15.75" customHeight="1">
+    <row r="974" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H974" s="3"/>
     </row>
-    <row r="975" ht="15.75" customHeight="1">
+    <row r="975" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H975" s="3"/>
     </row>
-    <row r="976" ht="15.75" customHeight="1">
+    <row r="976" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H976" s="3"/>
     </row>
-    <row r="977" ht="15.75" customHeight="1">
+    <row r="977" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H977" s="3"/>
     </row>
-    <row r="978" ht="15.75" customHeight="1">
+    <row r="978" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H978" s="3"/>
     </row>
-    <row r="979" ht="15.75" customHeight="1">
+    <row r="979" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H979" s="3"/>
     </row>
-    <row r="980" ht="15.75" customHeight="1">
+    <row r="980" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H980" s="3"/>
     </row>
-    <row r="981" ht="15.75" customHeight="1">
+    <row r="981" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H981" s="3"/>
     </row>
-    <row r="982" ht="15.75" customHeight="1">
+    <row r="982" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H982" s="3"/>
     </row>
-    <row r="983" ht="15.75" customHeight="1">
+    <row r="983" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H983" s="3"/>
     </row>
-    <row r="984" ht="15.75" customHeight="1">
+    <row r="984" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H984" s="3"/>
     </row>
-    <row r="985" ht="15.75" customHeight="1">
+    <row r="985" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H985" s="3"/>
     </row>
-    <row r="986" ht="15.75" customHeight="1">
+    <row r="986" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H986" s="3"/>
     </row>
-    <row r="987" ht="15.75" customHeight="1">
+    <row r="987" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H987" s="3"/>
     </row>
-    <row r="988" ht="15.75" customHeight="1">
+    <row r="988" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H988" s="3"/>
     </row>
-    <row r="989" ht="15.75" customHeight="1">
+    <row r="989" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H989" s="3"/>
     </row>
-    <row r="990" ht="15.75" customHeight="1">
+    <row r="990" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H990" s="3"/>
     </row>
-    <row r="991" ht="15.75" customHeight="1">
+    <row r="991" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H991" s="3"/>
     </row>
-    <row r="992" ht="15.75" customHeight="1">
+    <row r="992" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H992" s="3"/>
     </row>
-    <row r="993" ht="15.75" customHeight="1">
+    <row r="993" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H993" s="3"/>
     </row>
-    <row r="994" ht="15.75" customHeight="1">
+    <row r="994" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H994" s="3"/>
     </row>
-    <row r="995" ht="15.75" customHeight="1">
+    <row r="995" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H995" s="3"/>
     </row>
-    <row r="996" ht="15.75" customHeight="1">
+    <row r="996" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H996" s="3"/>
     </row>
-    <row r="997" ht="15.75" customHeight="1">
+    <row r="997" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H997" s="3"/>
     </row>
-    <row r="998" ht="15.75" customHeight="1">
+    <row r="998" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H998" s="3"/>
     </row>
-    <row r="999" ht="15.75" customHeight="1">
+    <row r="999" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H999" s="3"/>
     </row>
-    <row r="1000" ht="15.75" customHeight="1">
+    <row r="1000" spans="8:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H1000" s="3"/>
     </row>
   </sheetData>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
 </worksheet>
 </file>
--- a/docs/StatusTracker.xlsx
+++ b/docs/StatusTracker.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaushikyadala/Documents/IIIT/Fourth_Sem/DASS/Project/project-monorepo-team-35/docs/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D80CB1-E249-A14A-8AF4-96DEFA4D3C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="200" yWindow="1000" windowWidth="35600" windowHeight="22180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -232,39 +241,42 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -275,7 +287,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -309,99 +321,96 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -591,30 +600,33 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="42.13"/>
-    <col customWidth="1" min="2" max="2" width="73.63"/>
-    <col customWidth="1" min="3" max="3" width="17.75"/>
-    <col customWidth="1" min="7" max="7" width="77.63"/>
-    <col customWidth="1" min="8" max="8" width="18.38"/>
-    <col customWidth="1" min="9" max="9" width="17.38"/>
+    <col min="1" max="1" width="42.1640625" customWidth="1"/>
+    <col min="2" max="2" width="73.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="7" max="7" width="77.6640625" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -622,11 +634,11 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -641,7 +653,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -656,7 +668,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -685,7 +697,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
@@ -698,7 +710,7 @@
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="11" t="s">
         <v>15</v>
       </c>
@@ -723,7 +735,7 @@
       </c>
       <c r="I6" s="10"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="11" t="s">
         <v>19</v>
       </c>
@@ -734,7 +746,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="12">
         <v>0.5</v>
@@ -750,7 +762,7 @@
       </c>
       <c r="I7" s="10"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="11" t="s">
         <v>22</v>
       </c>
@@ -761,7 +773,7 @@
         <v>24</v>
       </c>
       <c r="D8" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="12">
         <v>0.75</v>
@@ -775,7 +787,7 @@
       </c>
       <c r="I8" s="10"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -789,7 +801,7 @@
         <v>1.5</v>
       </c>
       <c r="E9" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>18</v>
@@ -800,7 +812,7 @@
       </c>
       <c r="I9" s="10"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="11" t="s">
         <v>27</v>
       </c>
@@ -825,7 +837,7 @@
       </c>
       <c r="I10" s="10"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -836,7 +848,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
@@ -852,7 +864,7 @@
       </c>
       <c r="I11" s="10"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
         <v>31</v>
       </c>
@@ -863,11 +875,11 @@
       <c r="F12" s="9"/>
       <c r="G12" s="8"/>
       <c r="H12" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I12" s="10"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="11" t="s">
         <v>19</v>
       </c>
@@ -892,7 +904,7 @@
       </c>
       <c r="I13" s="10"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -917,7 +929,7 @@
       </c>
       <c r="I14" s="10"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="11" t="s">
         <v>33</v>
       </c>
@@ -938,11 +950,11 @@
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="11" t="s">
         <v>35</v>
       </c>
@@ -967,7 +979,7 @@
       </c>
       <c r="I16" s="10"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -994,7 +1006,7 @@
       </c>
       <c r="I17" s="10"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
@@ -1005,11 +1017,11 @@
       <c r="F18" s="9"/>
       <c r="G18" s="8"/>
       <c r="H18" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I18" s="10"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="11" t="s">
         <v>19</v>
       </c>
@@ -1020,7 +1032,7 @@
         <v>32</v>
       </c>
       <c r="D19" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="12">
         <v>1.25</v>
@@ -1036,7 +1048,7 @@
       </c>
       <c r="I19" s="10"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="11" t="s">
         <v>27</v>
       </c>
@@ -1061,7 +1073,7 @@
       </c>
       <c r="I20" s="10"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -1075,7 +1087,7 @@
         <v>0.75</v>
       </c>
       <c r="E21" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="13" t="s">
         <v>18</v>
@@ -1086,7 +1098,7 @@
       </c>
       <c r="I21" s="10"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="11" t="s">
         <v>39</v>
       </c>
@@ -1097,7 +1109,7 @@
         <v>28</v>
       </c>
       <c r="D22" s="12">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="12">
         <v>1.75</v>
@@ -1111,7 +1123,7 @@
       </c>
       <c r="I22" s="10"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="11" t="s">
         <v>40</v>
       </c>
@@ -1122,21 +1134,21 @@
         <v>24</v>
       </c>
       <c r="D23" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="12">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>18</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="7">
-        <v>-1.0</v>
+        <v>-1</v>
       </c>
       <c r="I23" s="15"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="5" t="s">
         <v>41</v>
       </c>
@@ -1149,22 +1161,22 @@
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="11" t="s">
         <v>42</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
       <c r="G25" s="3"/>
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="12" t="s">
         <v>43</v>
       </c>
@@ -1173,21 +1185,21 @@
         <v>17</v>
       </c>
       <c r="D26" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="13" t="s">
         <v>18</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I26" s="15"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="12" t="s">
         <v>44</v>
       </c>
@@ -1196,7 +1208,7 @@
         <v>28</v>
       </c>
       <c r="D27" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="12">
         <v>1.25</v>
@@ -1210,7 +1222,7 @@
       </c>
       <c r="I27" s="15"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12" t="s">
         <v>45</v>
       </c>
@@ -1219,7 +1231,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="12">
         <v>1.5</v>
@@ -1233,7 +1245,7 @@
       </c>
       <c r="I28" s="15"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="12" t="s">
         <v>46</v>
       </c>
@@ -1242,7 +1254,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="12">
         <v>1.5</v>
@@ -1256,7 +1268,7 @@
       </c>
       <c r="I29" s="15"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="12" t="s">
         <v>47</v>
       </c>
@@ -1265,10 +1277,10 @@
         <v>26</v>
       </c>
       <c r="D30" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="14">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>18</v>
@@ -1277,7 +1289,7 @@
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="12" t="s">
         <v>48</v>
       </c>
@@ -1298,11 +1310,11 @@
         <v>49</v>
       </c>
       <c r="H31" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I31" s="10"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="11" t="s">
         <v>50</v>
       </c>
@@ -1316,7 +1328,7 @@
         <v>1.5</v>
       </c>
       <c r="E32" s="12">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="13" t="s">
         <v>18</v>
@@ -1327,7 +1339,7 @@
       </c>
       <c r="I32" s="10"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="11" t="s">
         <v>52</v>
       </c>
@@ -1352,20 +1364,20 @@
       </c>
       <c r="I33" s="10"/>
     </row>
-    <row r="34">
-      <c r="A34" s="17" t="s">
+    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="18"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="17"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="11" t="s">
         <v>54</v>
       </c>
@@ -1379,7 +1391,7 @@
         <v>1.5</v>
       </c>
       <c r="E35" s="12">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F35" s="13" t="s">
         <v>18</v>
@@ -1390,7 +1402,7 @@
       </c>
       <c r="I35" s="10"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="11" t="s">
         <v>56</v>
       </c>
@@ -1415,7 +1427,7 @@
       </c>
       <c r="I36" s="10"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="11" t="s">
         <v>57</v>
       </c>
@@ -1440,7 +1452,7 @@
       </c>
       <c r="I37" s="10"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="11" t="s">
         <v>58</v>
       </c>
@@ -1461,11 +1473,11 @@
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I38" s="10"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="11" t="s">
         <v>59</v>
       </c>
@@ -1479,7 +1491,7 @@
         <v>1.5</v>
       </c>
       <c r="E39" s="12">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F39" s="13" t="s">
         <v>18</v>
@@ -1490,7 +1502,7 @@
       </c>
       <c r="I39" s="10"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="11" t="s">
         <v>27</v>
       </c>
@@ -1515,20 +1527,20 @@
       </c>
       <c r="I40" s="10"/>
     </row>
-    <row r="41">
-      <c r="A41" s="17" t="s">
+    <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="18"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="17"/>
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="11" t="s">
         <v>27</v>
       </c>
@@ -1553,7 +1565,7 @@
       </c>
       <c r="I42" s="10"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="11" t="s">
         <v>62</v>
       </c>
@@ -1564,7 +1576,7 @@
         <v>26</v>
       </c>
       <c r="D43" s="12">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E43" s="12">
         <v>1.5</v>
@@ -1578,20 +1590,20 @@
       </c>
       <c r="I43" s="10"/>
     </row>
-    <row r="44">
-      <c r="A44" s="17" t="s">
+    <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="18"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="18"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="17"/>
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="11" t="s">
         <v>64</v>
       </c>
@@ -1602,7 +1614,7 @@
         <v>28</v>
       </c>
       <c r="D45" s="12">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E45" s="12">
         <v>2.6</v>
@@ -1616,7 +1628,7 @@
       </c>
       <c r="I45" s="10"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="11" t="s">
         <v>66</v>
       </c>
@@ -1627,9 +1639,11 @@
         <v>24</v>
       </c>
       <c r="D46" s="12">
-        <v>2.0</v>
-      </c>
-      <c r="E46" s="12"/>
+        <v>2</v>
+      </c>
+      <c r="E46" s="12">
+        <v>2</v>
+      </c>
       <c r="F46" s="13" t="s">
         <v>18</v>
       </c>
@@ -1637,7 +1651,7 @@
       <c r="H46" s="7"/>
       <c r="I46" s="10"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="11" t="s">
         <v>67</v>
       </c>
@@ -1651,12 +1665,12 @@
         <v>2.5</v>
       </c>
       <c r="E47" s="12"/>
-      <c r="F47" s="20"/>
+      <c r="F47" s="19"/>
       <c r="G47" s="3"/>
       <c r="H47" s="7"/>
       <c r="I47" s="10"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="11" t="s">
         <v>68</v>
       </c>
@@ -1667,15 +1681,15 @@
         <v>24</v>
       </c>
       <c r="D48" s="12">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E48" s="12"/>
-      <c r="F48" s="20"/>
+      <c r="F48" s="19"/>
       <c r="G48" s="3"/>
       <c r="H48" s="7"/>
       <c r="I48" s="10"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="11" t="s">
         <v>69</v>
       </c>
@@ -1686,15 +1700,15 @@
         <v>20</v>
       </c>
       <c r="D49" s="12">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E49" s="12"/>
-      <c r="F49" s="20"/>
+      <c r="F49" s="19"/>
       <c r="G49" s="3"/>
       <c r="H49" s="7"/>
       <c r="I49" s="10"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="11" t="s">
         <v>70</v>
       </c>
@@ -1705,29 +1719,29 @@
         <v>26</v>
       </c>
       <c r="D50" s="12">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E50" s="12"/>
-      <c r="F50" s="20"/>
+      <c r="F50" s="19"/>
       <c r="G50" s="3"/>
       <c r="H50" s="7"/>
       <c r="I50" s="10"/>
     </row>
-    <row r="51">
-      <c r="A51" s="21" t="s">
+    <row r="51" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B51" s="21" t="s">
+      <c r="B51" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C51" s="22" t="s">
+      <c r="C51" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D51" s="22">
-        <v>3.0</v>
+      <c r="D51" s="14">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>